--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,54 +421,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -567,7 +555,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -596,7 +584,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -625,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -683,7 +671,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -712,7 +700,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -828,7 +816,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -944,7 +932,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +990,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1089,7 +1077,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1118,7 +1106,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1147,7 +1135,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1292,7 +1280,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1350,7 +1338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1379,7 +1367,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1408,7 +1396,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1553,7 +1541,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1582,7 +1570,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1611,7 +1599,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1640,7 +1628,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1669,7 +1657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1727,7 +1715,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1814,7 +1802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1843,7 +1831,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1872,7 +1860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1959,7 +1947,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1988,7 +1976,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2046,7 +2034,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2075,7 +2063,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2104,7 +2092,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2133,7 +2121,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2162,7 +2150,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2191,7 +2179,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2307,7 +2295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2336,7 +2324,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2365,7 +2353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2423,7 +2411,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2452,7 +2440,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2568,7 +2556,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2597,7 +2585,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2684,7 +2672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2713,7 +2701,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2771,7 +2759,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2800,7 +2788,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2887,7 +2875,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2945,7 +2933,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2974,7 +2962,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3032,7 +3020,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3061,7 +3049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3090,7 +3078,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3119,7 +3107,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3148,7 +3136,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3177,7 +3165,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3206,7 +3194,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3264,7 +3252,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3380,7 +3368,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3496,7 +3484,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3525,7 +3513,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3554,7 +3542,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3583,7 +3571,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3641,7 +3629,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3670,7 +3658,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3699,7 +3687,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3757,7 +3745,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3786,7 +3774,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3815,7 +3803,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3844,7 +3832,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3873,7 +3861,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3902,7 +3890,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3931,7 +3919,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3989,7 +3977,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4047,7 +4035,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4076,7 +4064,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4163,7 +4151,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4250,7 +4238,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4279,7 +4267,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4337,7 +4325,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4366,7 +4354,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4395,7 +4383,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4424,7 +4412,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4453,7 +4441,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4482,7 +4470,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4511,7 +4499,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4540,7 +4528,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4627,7 +4615,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4656,7 +4644,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4685,7 +4673,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4743,7 +4731,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4772,7 +4760,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4801,7 +4789,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4830,7 +4818,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4859,7 +4847,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4888,7 +4876,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4917,7 +4905,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -5004,7 +4992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5033,7 +5021,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5062,7 +5050,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5091,7 +5079,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5120,7 +5108,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5178,7 +5166,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5207,7 +5195,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5236,7 +5224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5294,7 +5282,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5323,7 +5311,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5352,7 +5340,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5410,7 +5398,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5439,7 +5427,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5468,7 +5456,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5497,7 +5485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5526,7 +5514,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5584,7 +5572,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5613,7 +5601,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5642,7 +5630,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5671,7 +5659,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5729,7 +5717,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5787,7 +5775,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5874,7 +5862,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5903,7 +5891,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5990,7 +5978,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6048,7 +6036,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6077,7 +6065,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6106,7 +6094,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6135,7 +6123,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6164,7 +6152,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6193,7 +6181,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6251,7 +6239,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6280,7 +6268,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6309,7 +6297,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6367,7 +6355,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6396,7 +6384,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6454,7 +6442,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6483,7 +6471,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6512,7 +6500,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6570,7 +6558,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6599,7 +6587,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6628,7 +6616,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6657,7 +6645,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6686,7 +6674,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6715,7 +6703,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6744,7 +6732,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6773,7 +6761,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6802,7 +6790,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6831,7 +6819,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6860,7 +6848,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6947,7 +6935,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6976,7 +6964,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -7005,7 +6993,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7034,7 +7022,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7063,7 +7051,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7150,7 +7138,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7237,7 +7225,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7266,7 +7254,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7324,7 +7312,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7353,7 +7341,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7382,7 +7370,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7411,7 +7399,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7440,7 +7428,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7469,7 +7457,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7527,7 +7515,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7585,7 +7573,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7614,7 +7602,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7643,7 +7631,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7672,7 +7660,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7730,7 +7718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7759,7 +7747,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7788,7 +7776,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7846,7 +7834,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7875,7 +7863,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7904,7 +7892,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7962,7 +7950,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7991,7 +7979,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8020,7 +8008,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8049,7 +8037,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8078,7 +8066,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8107,7 +8095,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8165,7 +8153,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8194,7 +8182,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8223,7 +8211,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8252,7 +8240,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8310,7 +8298,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8339,7 +8327,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8426,7 +8414,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8484,7 +8472,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8513,7 +8501,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8542,7 +8530,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8600,7 +8588,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8629,7 +8617,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8658,7 +8646,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8687,7 +8675,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8716,7 +8704,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8745,7 +8733,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8803,7 +8791,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8832,7 +8820,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8861,7 +8849,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8890,7 +8878,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8919,7 +8907,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -9006,7 +8994,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9035,7 +9023,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9122,7 +9110,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9151,7 +9139,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9180,7 +9168,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9209,7 +9197,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9238,7 +9226,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9267,7 +9255,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9296,7 +9284,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9325,7 +9313,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9354,7 +9342,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9383,7 +9371,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9412,7 +9400,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9441,7 +9429,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9470,7 +9458,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9499,7 +9487,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9528,7 +9516,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9557,7 +9545,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9586,7 +9574,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9615,7 +9603,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9731,7 +9719,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9760,7 +9748,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9789,7 +9777,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9818,7 +9806,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9876,7 +9864,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9905,7 +9893,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9934,7 +9922,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9963,7 +9951,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9992,7 +9980,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10021,7 +10009,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10079,7 +10067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10108,7 +10096,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10137,7 +10125,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10195,7 +10183,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10224,7 +10212,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10282,7 +10270,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10311,7 +10299,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10369,7 +10357,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10456,7 +10444,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10485,7 +10473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10514,7 +10502,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10543,7 +10531,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10572,7 +10560,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10630,7 +10618,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10659,7 +10647,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10688,7 +10676,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10717,7 +10705,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10746,7 +10734,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10775,7 +10763,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10804,7 +10792,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10833,7 +10821,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10862,7 +10850,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10891,7 +10879,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10978,7 +10966,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11036,7 +11024,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11065,7 +11053,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11094,7 +11082,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11152,7 +11140,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11181,7 +11169,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11210,7 +11198,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11239,7 +11227,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11268,7 +11256,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11297,7 +11285,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11355,7 +11343,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11384,7 +11372,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11413,7 +11401,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11442,7 +11430,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11471,7 +11459,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11500,7 +11488,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11558,7 +11546,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11587,7 +11575,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11616,7 +11604,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11645,7 +11633,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11674,7 +11662,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11703,7 +11691,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11732,7 +11720,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11761,7 +11749,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11877,7 +11865,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11906,7 +11894,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11935,7 +11923,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11993,7 +11981,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12022,7 +12010,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12051,7 +12039,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12080,7 +12068,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12109,7 +12097,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12138,7 +12126,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12167,7 +12155,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12225,7 +12213,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12254,7 +12242,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12283,7 +12271,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12312,7 +12300,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12341,7 +12329,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12370,7 +12358,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12428,7 +12416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12457,7 +12445,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12486,7 +12474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12515,7 +12503,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12573,7 +12561,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12631,7 +12619,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12660,7 +12648,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12689,7 +12677,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12718,7 +12706,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12747,7 +12735,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12776,7 +12764,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12834,7 +12822,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12863,7 +12851,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12892,7 +12880,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12921,7 +12909,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12950,7 +12938,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12979,7 +12967,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -13008,7 +12996,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13037,7 +13025,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13066,7 +13054,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13095,7 +13083,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13240,7 +13228,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13269,7 +13257,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13298,7 +13286,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13327,7 +13315,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13356,7 +13344,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13385,7 +13373,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13414,7 +13402,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13501,7 +13489,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13530,7 +13518,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13559,7 +13547,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13588,7 +13576,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13617,7 +13605,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13646,7 +13634,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13704,7 +13692,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13733,7 +13721,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13762,7 +13750,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13820,7 +13808,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13849,7 +13837,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13907,7 +13895,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13936,7 +13924,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13965,7 +13953,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13994,7 +13982,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14023,7 +14011,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14052,7 +14040,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14110,7 +14098,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14139,7 +14127,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14168,7 +14156,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14197,7 +14185,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14226,7 +14214,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14255,7 +14243,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14313,7 +14301,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14342,7 +14330,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14371,7 +14359,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14400,7 +14388,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14429,7 +14417,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14458,7 +14446,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14487,7 +14475,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14545,7 +14533,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14574,7 +14562,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14603,7 +14591,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14661,7 +14649,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14719,7 +14707,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14777,7 +14765,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14806,7 +14794,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14835,7 +14823,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14864,7 +14852,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14893,7 +14881,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14922,7 +14910,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14980,7 +14968,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -15009,7 +14997,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15038,7 +15026,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15067,7 +15055,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15096,7 +15084,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15125,7 +15113,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15183,7 +15171,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15212,7 +15200,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15241,7 +15229,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15270,7 +15258,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15299,7 +15287,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15328,7 +15316,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15386,7 +15374,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15415,7 +15403,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15444,7 +15432,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15473,7 +15461,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15502,7 +15490,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15531,7 +15519,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15560,7 +15548,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15589,7 +15577,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15618,7 +15606,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15647,7 +15635,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15676,7 +15664,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15705,7 +15693,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15734,7 +15722,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15763,7 +15751,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15792,7 +15780,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15821,7 +15809,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15850,7 +15838,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15908,7 +15896,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15966,7 +15954,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15995,7 +15983,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16053,7 +16041,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16111,7 +16099,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16140,7 +16128,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16169,7 +16157,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16198,7 +16186,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16256,7 +16244,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16285,7 +16273,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16314,7 +16302,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16343,7 +16331,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16372,7 +16360,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16401,7 +16389,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16430,7 +16418,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16459,7 +16447,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16488,7 +16476,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16517,7 +16505,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16546,7 +16534,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16575,7 +16563,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16604,7 +16592,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16633,7 +16621,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16662,7 +16650,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16691,7 +16679,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16778,7 +16766,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16807,7 +16795,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16836,7 +16824,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16894,7 +16882,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16923,7 +16911,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -17010,7 +16998,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17039,7 +17027,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17068,7 +17056,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17097,7 +17085,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17126,7 +17114,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17184,7 +17172,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17213,7 +17201,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17271,7 +17259,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17300,7 +17288,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17329,7 +17317,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17358,7 +17346,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17387,7 +17375,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17445,7 +17433,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17474,7 +17462,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17503,7 +17491,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17532,7 +17520,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17561,7 +17549,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17590,7 +17578,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17619,7 +17607,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17648,7 +17636,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17677,7 +17665,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17706,7 +17694,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17735,7 +17723,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17764,7 +17752,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17793,7 +17781,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17851,7 +17839,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17880,7 +17868,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,54 +433,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -671,7 +683,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -903,7 +915,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -932,7 +944,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1106,7 +1118,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1135,7 +1147,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1222,7 +1234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1280,7 +1292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1367,7 +1379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1715,7 +1727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1976,7 +1988,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2034,7 +2046,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2063,7 +2075,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2266,7 +2278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2527,7 +2539,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2672,7 +2684,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2701,7 +2713,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2962,7 +2974,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3107,7 +3119,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3136,7 +3148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3339,7 +3351,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3397,7 +3409,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3426,7 +3438,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3542,7 +3554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3571,7 +3583,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3629,7 +3641,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3687,7 +3699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3774,7 +3786,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3803,7 +3815,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3919,7 +3931,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3977,7 +3989,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4006,7 +4018,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4035,7 +4047,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4064,7 +4076,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4296,7 +4308,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4441,7 +4453,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4470,7 +4482,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4499,7 +4511,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4528,7 +4540,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4586,7 +4598,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4615,7 +4627,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4644,7 +4656,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4789,7 +4801,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4818,7 +4830,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4905,7 +4917,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -4992,7 +5004,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5021,7 +5033,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5050,7 +5062,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5224,7 +5236,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5253,7 +5265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5311,7 +5323,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5369,7 +5381,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5630,7 +5642,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5688,7 +5700,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6094,7 +6106,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6152,7 +6164,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6384,7 +6396,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6442,7 +6454,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6500,7 +6512,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6645,7 +6657,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6819,7 +6831,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6848,7 +6860,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7225,7 +7237,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7254,7 +7266,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7312,7 +7324,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7341,7 +7353,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7370,7 +7382,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7428,7 +7440,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7457,7 +7469,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7515,7 +7527,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7573,7 +7585,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7631,7 +7643,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7718,7 +7730,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7747,7 +7759,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7776,7 +7788,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7805,7 +7817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7834,7 +7846,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7863,7 +7875,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7892,7 +7904,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7921,7 +7933,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7979,7 +7991,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8037,7 +8049,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8095,7 +8107,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8153,7 +8165,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8182,7 +8194,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8211,7 +8223,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8240,7 +8252,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8298,7 +8310,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8327,7 +8339,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8414,7 +8426,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8443,7 +8455,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8472,7 +8484,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8501,7 +8513,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8530,7 +8542,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8617,7 +8629,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8646,7 +8658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8675,7 +8687,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8704,7 +8716,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8791,7 +8803,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8820,7 +8832,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8849,7 +8861,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8878,7 +8890,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8907,7 +8919,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -8994,7 +9006,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9023,7 +9035,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9081,7 +9093,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9168,7 +9180,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9226,7 +9238,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9255,7 +9267,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9284,7 +9296,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9313,7 +9325,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9342,7 +9354,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9371,7 +9383,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9400,7 +9412,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9429,7 +9441,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9487,7 +9499,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9545,7 +9557,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9574,7 +9586,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9603,7 +9615,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9719,7 +9731,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9777,7 +9789,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9864,7 +9876,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9893,7 +9905,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9922,7 +9934,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9951,7 +9963,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10009,7 +10021,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10067,7 +10079,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10096,7 +10108,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10125,7 +10137,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10154,7 +10166,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10212,7 +10224,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10299,7 +10311,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10357,7 +10369,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10444,7 +10456,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10531,7 +10543,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10560,7 +10572,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10589,7 +10601,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10618,7 +10630,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10647,7 +10659,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10705,7 +10717,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10763,7 +10775,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10792,7 +10804,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10821,7 +10833,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10850,7 +10862,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10879,7 +10891,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10937,7 +10949,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10966,7 +10978,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -10995,7 +11007,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11024,7 +11036,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11053,7 +11065,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11082,7 +11094,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11140,7 +11152,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11198,7 +11210,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11256,7 +11268,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11285,7 +11297,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11343,7 +11355,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11372,7 +11384,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11401,7 +11413,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11430,7 +11442,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11459,7 +11471,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11488,7 +11500,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11546,7 +11558,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11575,7 +11587,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11604,7 +11616,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11691,7 +11703,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11720,7 +11732,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11749,7 +11761,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11807,7 +11819,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11865,7 +11877,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11894,7 +11906,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11952,7 +11964,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11981,7 +11993,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12039,7 +12051,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12068,7 +12080,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12097,7 +12109,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12126,7 +12138,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12213,7 +12225,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12242,7 +12254,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12271,7 +12283,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12300,7 +12312,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12329,7 +12341,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12416,7 +12428,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12445,7 +12457,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12474,7 +12486,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12503,7 +12515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12532,7 +12544,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12561,7 +12573,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12619,7 +12631,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12648,7 +12660,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12677,7 +12689,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12735,7 +12747,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12764,7 +12776,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12822,7 +12834,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12851,7 +12863,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12880,7 +12892,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12909,7 +12921,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12938,7 +12950,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12967,7 +12979,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -12996,7 +13008,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13025,7 +13037,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13054,7 +13066,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13112,7 +13124,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13199,7 +13211,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13228,7 +13240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13257,7 +13269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13286,7 +13298,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13344,7 +13356,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13373,7 +13385,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13402,7 +13414,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13431,7 +13443,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13518,7 +13530,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13576,7 +13588,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13605,7 +13617,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13634,7 +13646,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13692,7 +13704,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13721,7 +13733,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13750,7 +13762,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13837,7 +13849,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13924,7 +13936,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13953,7 +13965,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13982,7 +13994,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14040,7 +14052,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14098,7 +14110,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14127,7 +14139,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14156,7 +14168,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14185,7 +14197,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14214,7 +14226,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14272,7 +14284,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14301,7 +14313,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14330,7 +14342,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14359,7 +14371,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14388,7 +14400,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14417,7 +14429,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14446,7 +14458,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14475,7 +14487,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14562,7 +14574,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14591,7 +14603,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14649,7 +14661,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14678,7 +14690,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14707,7 +14719,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14765,7 +14777,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14794,7 +14806,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14823,7 +14835,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14852,7 +14864,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14881,7 +14893,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14910,7 +14922,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14968,7 +14980,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -14997,7 +15009,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15026,7 +15038,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15055,7 +15067,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15171,7 +15183,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15200,7 +15212,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15229,7 +15241,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15287,7 +15299,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15316,7 +15328,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15374,7 +15386,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15403,7 +15415,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15432,7 +15444,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15461,7 +15473,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15490,7 +15502,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15519,7 +15531,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15548,7 +15560,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15577,7 +15589,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15606,7 +15618,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15635,7 +15647,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15664,7 +15676,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15693,7 +15705,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15722,7 +15734,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15751,7 +15763,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15780,7 +15792,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15809,7 +15821,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15838,7 +15850,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15896,7 +15908,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15925,7 +15937,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15954,7 +15966,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15983,7 +15995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16041,7 +16053,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16099,7 +16111,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16128,7 +16140,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16157,7 +16169,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16186,7 +16198,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16244,7 +16256,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16302,7 +16314,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16331,7 +16343,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16360,7 +16372,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16389,7 +16401,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16418,7 +16430,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16447,7 +16459,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16476,7 +16488,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16505,7 +16517,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16534,7 +16546,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16563,7 +16575,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16592,7 +16604,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16621,7 +16633,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16650,7 +16662,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16679,7 +16691,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16708,7 +16720,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16766,7 +16778,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16795,7 +16807,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16824,7 +16836,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16853,7 +16865,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16882,7 +16894,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16911,7 +16923,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16969,7 +16981,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -16998,7 +17010,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17027,7 +17039,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17056,7 +17068,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17085,7 +17097,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17172,7 +17184,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17201,7 +17213,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17288,7 +17300,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17317,7 +17329,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17346,7 +17358,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17375,7 +17387,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17433,7 +17445,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17491,7 +17503,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17520,7 +17532,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17549,7 +17561,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17578,7 +17590,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17607,7 +17619,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17636,7 +17648,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17665,7 +17677,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17723,7 +17735,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17752,7 +17764,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17781,7 +17793,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17839,7 +17851,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17868,7 +17880,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I602"/>
+  <dimension ref="A1:I603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17908,6 +17908,35 @@
         <v>35.597</v>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B603" t="n">
+        <v>692.949958</v>
+      </c>
+      <c r="C603" t="n">
+        <v>-652.153468</v>
+      </c>
+      <c r="D603" t="n">
+        <v>1345.103426</v>
+      </c>
+      <c r="E603" t="n">
+        <v>-378.63</v>
+      </c>
+      <c r="F603" t="n">
+        <v>-273.523468</v>
+      </c>
+      <c r="G603" t="n">
+        <v>-119.771</v>
+      </c>
+      <c r="H603" t="n">
+        <v>-156.646468</v>
+      </c>
+      <c r="I603" t="n">
+        <v>2.894</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,54 +421,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -567,7 +555,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -596,7 +584,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -625,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -683,7 +671,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -712,7 +700,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -828,7 +816,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -944,7 +932,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +990,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1089,7 +1077,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1118,7 +1106,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1147,7 +1135,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1292,7 +1280,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1350,7 +1338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1379,7 +1367,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1408,7 +1396,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1553,7 +1541,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1582,7 +1570,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1611,7 +1599,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1640,7 +1628,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1669,7 +1657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1727,7 +1715,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1814,7 +1802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1843,7 +1831,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1872,7 +1860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1959,7 +1947,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1988,7 +1976,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2046,7 +2034,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2075,7 +2063,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2104,7 +2092,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2133,7 +2121,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2162,7 +2150,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2191,7 +2179,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2307,7 +2295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2336,7 +2324,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2365,7 +2353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2423,7 +2411,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2452,7 +2440,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2568,7 +2556,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2597,7 +2585,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2684,7 +2672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2713,7 +2701,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2771,7 +2759,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2800,7 +2788,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2887,7 +2875,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2945,7 +2933,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2974,7 +2962,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3032,7 +3020,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3061,7 +3049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3090,7 +3078,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3119,7 +3107,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3148,7 +3136,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3177,7 +3165,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3206,7 +3194,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3264,7 +3252,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3380,7 +3368,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3496,7 +3484,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3525,7 +3513,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3554,7 +3542,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3583,7 +3571,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3641,7 +3629,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3670,7 +3658,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3699,7 +3687,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3757,7 +3745,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3786,7 +3774,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3815,7 +3803,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3844,7 +3832,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3873,7 +3861,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3902,7 +3890,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3931,7 +3919,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3989,7 +3977,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4047,7 +4035,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4076,7 +4064,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4163,7 +4151,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4250,7 +4238,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4279,7 +4267,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4337,7 +4325,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4366,7 +4354,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4395,7 +4383,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4424,7 +4412,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4453,7 +4441,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4482,7 +4470,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4511,7 +4499,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4540,7 +4528,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4627,7 +4615,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4656,7 +4644,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4685,7 +4673,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4743,7 +4731,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4772,7 +4760,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4801,7 +4789,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4830,7 +4818,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4859,7 +4847,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4888,7 +4876,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4917,7 +4905,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -5004,7 +4992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5033,7 +5021,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5062,7 +5050,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5091,7 +5079,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5120,7 +5108,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5178,7 +5166,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5207,7 +5195,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5236,7 +5224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5294,7 +5282,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5323,7 +5311,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5352,7 +5340,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5410,7 +5398,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5439,7 +5427,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5468,7 +5456,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5497,7 +5485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5526,7 +5514,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5584,7 +5572,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5613,7 +5601,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5642,7 +5630,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5671,7 +5659,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5729,7 +5717,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5787,7 +5775,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5874,7 +5862,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5903,7 +5891,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5990,7 +5978,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6048,7 +6036,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6077,7 +6065,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6106,7 +6094,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6135,7 +6123,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6164,7 +6152,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6193,7 +6181,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6251,7 +6239,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6280,7 +6268,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6309,7 +6297,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6367,7 +6355,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6396,7 +6384,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6454,7 +6442,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6483,7 +6471,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6512,7 +6500,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6570,7 +6558,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6599,7 +6587,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6628,7 +6616,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6657,7 +6645,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6686,7 +6674,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6715,7 +6703,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6744,7 +6732,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6773,7 +6761,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6802,7 +6790,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6831,7 +6819,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6860,7 +6848,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6947,7 +6935,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6976,7 +6964,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -7005,7 +6993,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7034,7 +7022,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7063,7 +7051,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7150,7 +7138,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7237,7 +7225,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7266,7 +7254,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7324,7 +7312,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7353,7 +7341,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7382,7 +7370,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7411,7 +7399,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7440,7 +7428,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7469,7 +7457,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7527,7 +7515,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7585,7 +7573,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7614,7 +7602,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7643,7 +7631,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7672,7 +7660,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7730,7 +7718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7759,7 +7747,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7788,7 +7776,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7846,7 +7834,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7875,7 +7863,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7904,7 +7892,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7962,7 +7950,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7991,7 +7979,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8020,7 +8008,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8049,7 +8037,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8078,7 +8066,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8107,7 +8095,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8165,7 +8153,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8194,7 +8182,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8223,7 +8211,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8252,7 +8240,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8310,7 +8298,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8339,7 +8327,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8426,7 +8414,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8484,7 +8472,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8513,7 +8501,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8542,7 +8530,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8600,7 +8588,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8629,7 +8617,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8658,7 +8646,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8687,7 +8675,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8716,7 +8704,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8745,7 +8733,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8803,7 +8791,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8832,7 +8820,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8861,7 +8849,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8890,7 +8878,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8919,7 +8907,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -9006,7 +8994,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9035,7 +9023,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9122,7 +9110,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9151,7 +9139,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9180,7 +9168,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9209,7 +9197,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9238,7 +9226,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9267,7 +9255,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9296,7 +9284,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9325,7 +9313,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9354,7 +9342,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9383,7 +9371,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9412,7 +9400,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9441,7 +9429,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9470,7 +9458,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9499,7 +9487,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9528,7 +9516,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9557,7 +9545,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9586,7 +9574,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9615,7 +9603,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9731,7 +9719,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9760,7 +9748,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9789,7 +9777,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9818,7 +9806,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9876,7 +9864,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9905,7 +9893,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9934,7 +9922,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9963,7 +9951,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9992,7 +9980,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10021,7 +10009,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10079,7 +10067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10108,7 +10096,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10137,7 +10125,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10195,7 +10183,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10224,7 +10212,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10282,7 +10270,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10311,7 +10299,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10369,7 +10357,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10456,7 +10444,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10485,7 +10473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10514,7 +10502,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10543,7 +10531,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10572,7 +10560,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10630,7 +10618,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10659,7 +10647,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10688,7 +10676,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10717,7 +10705,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10746,7 +10734,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10775,7 +10763,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10804,7 +10792,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10833,7 +10821,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10862,7 +10850,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10891,7 +10879,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10978,7 +10966,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11036,7 +11024,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11065,7 +11053,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11094,7 +11082,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11152,7 +11140,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11181,7 +11169,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11210,7 +11198,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11239,7 +11227,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11268,7 +11256,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11297,7 +11285,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11355,7 +11343,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11384,7 +11372,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11413,7 +11401,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11442,7 +11430,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11471,7 +11459,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11500,7 +11488,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11558,7 +11546,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11587,7 +11575,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11616,7 +11604,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11645,7 +11633,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11674,7 +11662,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11703,7 +11691,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11732,7 +11720,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11761,7 +11749,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11877,7 +11865,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11906,7 +11894,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11935,7 +11923,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11993,7 +11981,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12022,7 +12010,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12051,7 +12039,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12080,7 +12068,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12109,7 +12097,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12138,7 +12126,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12167,7 +12155,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12225,7 +12213,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12254,7 +12242,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12283,7 +12271,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12312,7 +12300,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12341,7 +12329,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12370,7 +12358,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12428,7 +12416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12457,7 +12445,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12486,7 +12474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12515,7 +12503,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12573,7 +12561,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12631,7 +12619,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12660,7 +12648,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12689,7 +12677,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12718,7 +12706,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12747,7 +12735,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12776,7 +12764,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12834,7 +12822,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12863,7 +12851,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12892,7 +12880,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12921,7 +12909,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12950,7 +12938,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12979,7 +12967,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -13008,7 +12996,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13037,7 +13025,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13066,7 +13054,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13095,7 +13083,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13240,7 +13228,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13269,7 +13257,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13298,7 +13286,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13327,7 +13315,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13356,7 +13344,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13385,7 +13373,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13414,7 +13402,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13501,7 +13489,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13530,7 +13518,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13559,7 +13547,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13588,7 +13576,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13617,7 +13605,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13646,7 +13634,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13704,7 +13692,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13733,7 +13721,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13762,7 +13750,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13820,7 +13808,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13849,7 +13837,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13907,7 +13895,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13936,7 +13924,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13965,7 +13953,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13994,7 +13982,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14023,7 +14011,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14052,7 +14040,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14110,7 +14098,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14139,7 +14127,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14168,7 +14156,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14197,7 +14185,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14226,7 +14214,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14255,7 +14243,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14313,7 +14301,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14342,7 +14330,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14371,7 +14359,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14400,7 +14388,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14429,7 +14417,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14458,7 +14446,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14487,7 +14475,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14545,7 +14533,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14574,7 +14562,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14603,7 +14591,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14661,7 +14649,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14719,7 +14707,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14777,7 +14765,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14806,7 +14794,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14835,7 +14823,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14864,7 +14852,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14893,7 +14881,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14922,7 +14910,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14980,7 +14968,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -15009,7 +14997,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15038,7 +15026,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15067,7 +15055,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15096,7 +15084,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15125,7 +15113,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15183,7 +15171,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15212,7 +15200,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15241,7 +15229,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15270,7 +15258,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15299,7 +15287,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15328,7 +15316,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15386,7 +15374,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15415,7 +15403,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15444,7 +15432,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15473,7 +15461,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15502,7 +15490,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15531,7 +15519,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15560,7 +15548,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15589,7 +15577,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15618,7 +15606,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15647,7 +15635,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15676,7 +15664,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15705,7 +15693,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15734,7 +15722,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15763,7 +15751,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15792,7 +15780,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15821,7 +15809,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15850,7 +15838,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15908,7 +15896,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15966,7 +15954,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15995,7 +15983,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16053,7 +16041,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16111,7 +16099,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16140,7 +16128,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16169,7 +16157,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16198,7 +16186,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16256,7 +16244,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16285,7 +16273,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16314,7 +16302,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16343,7 +16331,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16372,7 +16360,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16401,7 +16389,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16430,7 +16418,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16459,7 +16447,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16488,7 +16476,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16517,7 +16505,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16546,7 +16534,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16575,7 +16563,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16604,7 +16592,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16633,7 +16621,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16662,7 +16650,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16691,7 +16679,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16778,7 +16766,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16807,7 +16795,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16836,7 +16824,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16894,7 +16882,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16923,7 +16911,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -17010,7 +16998,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17039,7 +17027,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17068,7 +17056,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17097,7 +17085,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17126,7 +17114,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17184,7 +17172,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17213,7 +17201,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17271,7 +17259,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17300,7 +17288,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17329,7 +17317,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17358,7 +17346,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17387,7 +17375,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17445,7 +17433,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17474,7 +17462,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17503,7 +17491,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17532,7 +17520,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17561,7 +17549,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17590,7 +17578,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17619,7 +17607,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17648,7 +17636,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17677,7 +17665,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17706,7 +17694,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17735,7 +17723,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17764,7 +17752,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17793,7 +17781,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17851,7 +17839,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17880,7 +17868,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17909,7 +17897,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I603"/>
+  <dimension ref="A1:I604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17925,6 +17925,35 @@
         <v>2.894</v>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B604" t="n">
+        <v>5259.384625</v>
+      </c>
+      <c r="C604" t="n">
+        <v>-334.260137</v>
+      </c>
+      <c r="D604" t="n">
+        <v>5593.644762</v>
+      </c>
+      <c r="E604" t="n">
+        <v>-254.05</v>
+      </c>
+      <c r="F604" t="n">
+        <v>-80.210137</v>
+      </c>
+      <c r="G604" t="n">
+        <v>-42.893</v>
+      </c>
+      <c r="H604" t="n">
+        <v>-58.128137</v>
+      </c>
+      <c r="I604" t="n">
+        <v>20.811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I604"/>
+  <dimension ref="A1:I605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17954,6 +17954,35 @@
         <v>20.811</v>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B605" t="n">
+        <v>2360.519754</v>
+      </c>
+      <c r="C605" t="n">
+        <v>387.34562</v>
+      </c>
+      <c r="D605" t="n">
+        <v>1973.174134</v>
+      </c>
+      <c r="E605" t="n">
+        <v>263.987</v>
+      </c>
+      <c r="F605" t="n">
+        <v>123.35862</v>
+      </c>
+      <c r="G605" t="n">
+        <v>150.431</v>
+      </c>
+      <c r="H605" t="n">
+        <v>18.72862</v>
+      </c>
+      <c r="I605" t="n">
+        <v>-45.801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I605"/>
+  <dimension ref="A1:I606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17983,6 +17983,35 @@
         <v>-45.801</v>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B606" t="n">
+        <v>-3548.426043</v>
+      </c>
+      <c r="C606" t="n">
+        <v>-214.757483</v>
+      </c>
+      <c r="D606" t="n">
+        <v>-3333.66856</v>
+      </c>
+      <c r="E606" t="n">
+        <v>-137.958</v>
+      </c>
+      <c r="F606" t="n">
+        <v>-76.799483</v>
+      </c>
+      <c r="G606" t="n">
+        <v>-103.439</v>
+      </c>
+      <c r="H606" t="n">
+        <v>-0.051483</v>
+      </c>
+      <c r="I606" t="n">
+        <v>26.691</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I606"/>
+  <dimension ref="A1:I607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17466,28 +17466,28 @@
         <v>46108</v>
       </c>
       <c r="B588" t="n">
-        <v>2210.512691</v>
+        <v>2216.189624</v>
       </c>
       <c r="C588" t="n">
-        <v>1831.064616</v>
+        <v>1832.606559</v>
       </c>
       <c r="D588" t="n">
-        <v>379.448075</v>
+        <v>383.583065</v>
       </c>
       <c r="E588" t="n">
-        <v>1863.709</v>
+        <v>1865.105</v>
       </c>
       <c r="F588" t="n">
-        <v>-32.644384</v>
+        <v>-32.498441</v>
       </c>
       <c r="G588" t="n">
-        <v>55.256</v>
+        <v>55.411</v>
       </c>
       <c r="H588" t="n">
-        <v>-157.941384</v>
+        <v>-157.949441</v>
       </c>
       <c r="I588" t="n">
-        <v>70.041</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="589">
@@ -18010,6 +18010,35 @@
       </c>
       <c r="I606" t="n">
         <v>26.691</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B607" t="n">
+        <v>1770.35629</v>
+      </c>
+      <c r="C607" t="n">
+        <v>1402.625228</v>
+      </c>
+      <c r="D607" t="n">
+        <v>367.731062</v>
+      </c>
+      <c r="E607" t="n">
+        <v>480.05</v>
+      </c>
+      <c r="F607" t="n">
+        <v>922.575228</v>
+      </c>
+      <c r="G607" t="n">
+        <v>929.888</v>
+      </c>
+      <c r="H607" t="n">
+        <v>-32.072772</v>
+      </c>
+      <c r="I607" t="n">
+        <v>24.76</v>
       </c>
     </row>
   </sheetData>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,54 +433,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -671,7 +683,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -903,7 +915,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -932,7 +944,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1106,7 +1118,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1135,7 +1147,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1222,7 +1234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1280,7 +1292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1367,7 +1379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1715,7 +1727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1976,7 +1988,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2034,7 +2046,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2063,7 +2075,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2266,7 +2278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2527,7 +2539,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2672,7 +2684,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2701,7 +2713,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2962,7 +2974,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3107,7 +3119,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3136,7 +3148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3339,7 +3351,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3397,7 +3409,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3426,7 +3438,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3542,7 +3554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3571,7 +3583,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3629,7 +3641,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3687,7 +3699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3774,7 +3786,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3803,7 +3815,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3919,7 +3931,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3977,7 +3989,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4006,7 +4018,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4035,7 +4047,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4064,7 +4076,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4296,7 +4308,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4441,7 +4453,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4470,7 +4482,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4499,7 +4511,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4528,7 +4540,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4586,7 +4598,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4615,7 +4627,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4644,7 +4656,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4789,7 +4801,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4818,7 +4830,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4905,7 +4917,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -4992,7 +5004,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5021,7 +5033,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5050,7 +5062,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5224,7 +5236,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5253,7 +5265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5311,7 +5323,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5369,7 +5381,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5630,7 +5642,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5688,7 +5700,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6094,7 +6106,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6152,7 +6164,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6384,7 +6396,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6442,7 +6454,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6500,7 +6512,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6645,7 +6657,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6819,7 +6831,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6848,7 +6860,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7225,7 +7237,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7254,7 +7266,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7312,7 +7324,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7341,7 +7353,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7370,7 +7382,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7428,7 +7440,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7457,7 +7469,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7515,7 +7527,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7573,7 +7585,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7631,7 +7643,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7718,7 +7730,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7747,7 +7759,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7776,7 +7788,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7805,7 +7817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7834,7 +7846,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7863,7 +7875,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7892,7 +7904,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7921,7 +7933,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7979,7 +7991,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8037,7 +8049,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8095,7 +8107,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8153,7 +8165,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8182,7 +8194,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8211,7 +8223,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8240,7 +8252,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8298,7 +8310,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8327,7 +8339,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8414,7 +8426,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8443,7 +8455,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8472,7 +8484,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8501,7 +8513,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8530,7 +8542,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8617,7 +8629,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8646,7 +8658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8675,7 +8687,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8704,7 +8716,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8791,7 +8803,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8820,7 +8832,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8849,7 +8861,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8878,7 +8890,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8907,7 +8919,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -8994,7 +9006,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9023,7 +9035,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9081,7 +9093,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9168,7 +9180,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9226,7 +9238,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9255,7 +9267,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9284,7 +9296,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9313,7 +9325,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9342,7 +9354,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9371,7 +9383,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9400,7 +9412,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9429,7 +9441,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9487,7 +9499,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9545,7 +9557,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9574,7 +9586,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9603,7 +9615,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9719,7 +9731,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9777,7 +9789,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9864,7 +9876,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9893,7 +9905,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9922,7 +9934,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9951,7 +9963,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10009,7 +10021,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10067,7 +10079,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10096,7 +10108,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10125,7 +10137,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10154,7 +10166,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10212,7 +10224,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10299,7 +10311,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10357,7 +10369,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10444,7 +10456,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10531,7 +10543,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10560,7 +10572,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10589,7 +10601,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10618,7 +10630,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10647,7 +10659,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10705,7 +10717,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10763,7 +10775,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10792,7 +10804,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10821,7 +10833,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10850,7 +10862,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10879,7 +10891,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10937,7 +10949,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10966,7 +10978,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -10995,7 +11007,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11024,7 +11036,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11053,7 +11065,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11082,7 +11094,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11140,7 +11152,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11198,7 +11210,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11256,7 +11268,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11285,7 +11297,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11343,7 +11355,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11372,7 +11384,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11401,7 +11413,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11430,7 +11442,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11459,7 +11471,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11488,7 +11500,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11546,7 +11558,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11575,7 +11587,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11604,7 +11616,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11691,7 +11703,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11720,7 +11732,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11749,7 +11761,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11807,7 +11819,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11865,7 +11877,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11894,7 +11906,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11952,7 +11964,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11981,7 +11993,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12039,7 +12051,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12068,7 +12080,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12097,7 +12109,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12126,7 +12138,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12213,7 +12225,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12242,7 +12254,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12271,7 +12283,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12300,7 +12312,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12329,7 +12341,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12416,7 +12428,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12445,7 +12457,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12474,7 +12486,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12503,7 +12515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12532,7 +12544,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12561,7 +12573,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12619,7 +12631,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12648,7 +12660,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12677,7 +12689,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12735,7 +12747,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12764,7 +12776,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12822,7 +12834,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12851,7 +12863,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12880,7 +12892,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12909,7 +12921,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12938,7 +12950,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12967,7 +12979,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -12996,7 +13008,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13025,7 +13037,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13054,7 +13066,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13112,7 +13124,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13199,7 +13211,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13228,7 +13240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13257,7 +13269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13286,7 +13298,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13344,7 +13356,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13373,7 +13385,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13402,7 +13414,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13431,7 +13443,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13518,7 +13530,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13576,7 +13588,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13605,7 +13617,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13634,7 +13646,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13692,7 +13704,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13721,7 +13733,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13750,7 +13762,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13837,7 +13849,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13924,7 +13936,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13953,7 +13965,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13982,7 +13994,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14040,7 +14052,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14098,7 +14110,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14127,7 +14139,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14156,7 +14168,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14185,7 +14197,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14214,7 +14226,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14272,7 +14284,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14301,7 +14313,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14330,7 +14342,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14359,7 +14371,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14388,7 +14400,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14417,7 +14429,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14446,7 +14458,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14475,7 +14487,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14562,7 +14574,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14591,7 +14603,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14649,7 +14661,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14678,7 +14690,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14707,7 +14719,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14765,7 +14777,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14794,7 +14806,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14823,7 +14835,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14852,7 +14864,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14881,7 +14893,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14910,7 +14922,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14968,7 +14980,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -14997,7 +15009,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15026,7 +15038,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15055,7 +15067,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15171,7 +15183,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15200,7 +15212,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15229,7 +15241,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15287,7 +15299,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15316,7 +15328,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15374,7 +15386,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15403,7 +15415,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15432,7 +15444,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15461,7 +15473,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15490,7 +15502,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15519,7 +15531,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15548,7 +15560,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15577,7 +15589,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15606,7 +15618,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15635,7 +15647,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15664,7 +15676,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15693,7 +15705,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15722,7 +15734,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15751,7 +15763,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15780,7 +15792,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15809,7 +15821,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15838,7 +15850,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15896,7 +15908,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15925,7 +15937,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15954,7 +15966,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15983,7 +15995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16041,7 +16053,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16099,7 +16111,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16128,7 +16140,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16157,7 +16169,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16186,7 +16198,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16244,7 +16256,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16302,7 +16314,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16331,7 +16343,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16360,7 +16372,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16389,7 +16401,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16418,7 +16430,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16447,7 +16459,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16476,7 +16488,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16505,7 +16517,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16534,7 +16546,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16563,7 +16575,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16592,7 +16604,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16621,7 +16633,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16650,7 +16662,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16679,7 +16691,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16708,7 +16720,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16766,7 +16778,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16795,7 +16807,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16824,7 +16836,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16853,7 +16865,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16882,7 +16894,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16911,7 +16923,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16969,7 +16981,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -16998,7 +17010,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17027,7 +17039,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17056,7 +17068,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17085,7 +17097,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17172,7 +17184,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17201,7 +17213,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17288,7 +17300,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17317,7 +17329,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17346,7 +17358,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17375,7 +17387,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17433,7 +17445,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17491,7 +17503,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17520,7 +17532,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17549,7 +17561,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17578,7 +17590,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17607,7 +17619,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17636,7 +17648,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17665,7 +17677,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17723,7 +17735,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17752,7 +17764,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17781,7 +17793,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17839,7 +17851,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17868,7 +17880,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17897,7 +17909,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17926,7 +17938,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17955,7 +17967,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17984,7 +17996,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18013,7 +18025,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,54 +421,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -567,7 +555,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -596,7 +584,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -625,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -683,7 +671,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -712,7 +700,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -828,7 +816,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -944,7 +932,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +990,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1089,7 +1077,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1118,7 +1106,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1147,7 +1135,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1292,7 +1280,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1350,7 +1338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1379,7 +1367,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1408,7 +1396,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1553,7 +1541,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1582,7 +1570,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1611,7 +1599,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1640,7 +1628,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1669,7 +1657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1727,7 +1715,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1814,7 +1802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1843,7 +1831,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1872,7 +1860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1959,7 +1947,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1988,7 +1976,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2046,7 +2034,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2075,7 +2063,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2104,7 +2092,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2133,7 +2121,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2162,7 +2150,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2191,7 +2179,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2307,7 +2295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2336,7 +2324,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2365,7 +2353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2423,7 +2411,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2452,7 +2440,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2568,7 +2556,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2597,7 +2585,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2684,7 +2672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2713,7 +2701,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2771,7 +2759,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2800,7 +2788,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2887,7 +2875,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2945,7 +2933,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2974,7 +2962,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3032,7 +3020,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3061,7 +3049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3090,7 +3078,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3119,7 +3107,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3148,7 +3136,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3177,7 +3165,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3206,7 +3194,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3264,7 +3252,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3380,7 +3368,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3496,7 +3484,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3525,7 +3513,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3554,7 +3542,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3583,7 +3571,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3641,7 +3629,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3670,7 +3658,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3699,7 +3687,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3757,7 +3745,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3786,7 +3774,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3815,7 +3803,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3844,7 +3832,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3873,7 +3861,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3902,7 +3890,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3931,7 +3919,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3989,7 +3977,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4047,7 +4035,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4076,7 +4064,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4163,7 +4151,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4250,7 +4238,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4279,7 +4267,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4337,7 +4325,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4366,7 +4354,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4395,7 +4383,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4424,7 +4412,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4453,7 +4441,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4482,7 +4470,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4511,7 +4499,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4540,7 +4528,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4627,7 +4615,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4656,7 +4644,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4685,7 +4673,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4743,7 +4731,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4772,7 +4760,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4801,7 +4789,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4830,7 +4818,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4859,7 +4847,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4888,7 +4876,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4917,7 +4905,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -5004,7 +4992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5033,7 +5021,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5062,7 +5050,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5091,7 +5079,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5120,7 +5108,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5178,7 +5166,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5207,7 +5195,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5236,7 +5224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5294,7 +5282,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5323,7 +5311,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5352,7 +5340,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5410,7 +5398,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5439,7 +5427,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5468,7 +5456,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5497,7 +5485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5526,7 +5514,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5584,7 +5572,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5613,7 +5601,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5642,7 +5630,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5671,7 +5659,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5729,7 +5717,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5787,7 +5775,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5874,7 +5862,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5903,7 +5891,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5990,7 +5978,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6048,7 +6036,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6077,7 +6065,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6106,7 +6094,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6135,7 +6123,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6164,7 +6152,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6193,7 +6181,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6251,7 +6239,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6280,7 +6268,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6309,7 +6297,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6367,7 +6355,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6396,7 +6384,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6454,7 +6442,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6483,7 +6471,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6512,7 +6500,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6570,7 +6558,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6599,7 +6587,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6628,7 +6616,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6657,7 +6645,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6686,7 +6674,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6715,7 +6703,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6744,7 +6732,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6773,7 +6761,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6802,7 +6790,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6831,7 +6819,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6860,7 +6848,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6947,7 +6935,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6976,7 +6964,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -7005,7 +6993,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7034,7 +7022,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7063,7 +7051,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7150,7 +7138,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7237,7 +7225,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7266,7 +7254,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7324,7 +7312,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7353,7 +7341,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7382,7 +7370,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7411,7 +7399,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7440,7 +7428,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7469,7 +7457,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7527,7 +7515,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7585,7 +7573,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7614,7 +7602,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7643,7 +7631,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7672,7 +7660,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7730,7 +7718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7759,7 +7747,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7788,7 +7776,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7846,7 +7834,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7875,7 +7863,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7904,7 +7892,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7962,7 +7950,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7991,7 +7979,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8020,7 +8008,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8049,7 +8037,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8078,7 +8066,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8107,7 +8095,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8165,7 +8153,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8194,7 +8182,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8223,7 +8211,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8252,7 +8240,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8310,7 +8298,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8339,7 +8327,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8426,7 +8414,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8484,7 +8472,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8513,7 +8501,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8542,7 +8530,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8600,7 +8588,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8629,7 +8617,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8658,7 +8646,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8687,7 +8675,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8716,7 +8704,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8745,7 +8733,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8803,7 +8791,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8832,7 +8820,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8861,7 +8849,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8890,7 +8878,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8919,7 +8907,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -9006,7 +8994,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9035,7 +9023,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9122,7 +9110,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9151,7 +9139,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9180,7 +9168,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9209,7 +9197,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9238,7 +9226,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9267,7 +9255,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9296,7 +9284,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9325,7 +9313,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9354,7 +9342,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9383,7 +9371,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9412,7 +9400,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9441,7 +9429,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9470,7 +9458,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9499,7 +9487,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9528,7 +9516,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9557,7 +9545,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9586,7 +9574,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9615,7 +9603,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9731,7 +9719,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9760,7 +9748,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9789,7 +9777,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9818,7 +9806,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9876,7 +9864,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9905,7 +9893,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9934,7 +9922,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9963,7 +9951,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9992,7 +9980,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10021,7 +10009,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10079,7 +10067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10108,7 +10096,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10137,7 +10125,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10195,7 +10183,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10224,7 +10212,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10282,7 +10270,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10311,7 +10299,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10369,7 +10357,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10456,7 +10444,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10485,7 +10473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10514,7 +10502,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10543,7 +10531,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10572,7 +10560,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10630,7 +10618,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10659,7 +10647,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10688,7 +10676,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10717,7 +10705,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10746,7 +10734,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10775,7 +10763,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10804,7 +10792,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10833,7 +10821,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10862,7 +10850,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10891,7 +10879,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10978,7 +10966,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11036,7 +11024,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11065,7 +11053,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11094,7 +11082,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11152,7 +11140,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11181,7 +11169,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11210,7 +11198,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11239,7 +11227,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11268,7 +11256,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11297,7 +11285,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11355,7 +11343,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11384,7 +11372,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11413,7 +11401,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11442,7 +11430,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11471,7 +11459,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11500,7 +11488,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11558,7 +11546,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11587,7 +11575,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11616,7 +11604,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11645,7 +11633,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11674,7 +11662,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11703,7 +11691,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11732,7 +11720,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11761,7 +11749,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11877,7 +11865,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11906,7 +11894,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11935,7 +11923,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11993,7 +11981,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12022,7 +12010,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12051,7 +12039,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12080,7 +12068,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12109,7 +12097,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12138,7 +12126,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12167,7 +12155,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12225,7 +12213,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12254,7 +12242,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12283,7 +12271,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12312,7 +12300,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12341,7 +12329,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12370,7 +12358,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12428,7 +12416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12457,7 +12445,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12486,7 +12474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12515,7 +12503,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12573,7 +12561,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12631,7 +12619,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12660,7 +12648,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12689,7 +12677,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12718,7 +12706,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12747,7 +12735,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12776,7 +12764,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12834,7 +12822,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12863,7 +12851,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12892,7 +12880,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12921,7 +12909,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12950,7 +12938,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12979,7 +12967,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -13008,7 +12996,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13037,7 +13025,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13066,7 +13054,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13095,7 +13083,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13240,7 +13228,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13269,7 +13257,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13298,7 +13286,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13327,7 +13315,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13356,7 +13344,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13385,7 +13373,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13414,7 +13402,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13501,7 +13489,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13530,7 +13518,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13559,7 +13547,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13588,7 +13576,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13617,7 +13605,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13646,7 +13634,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13704,7 +13692,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13733,7 +13721,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13762,7 +13750,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13820,7 +13808,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13849,7 +13837,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13907,7 +13895,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13936,7 +13924,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13965,7 +13953,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13994,7 +13982,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14023,7 +14011,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14052,7 +14040,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14110,7 +14098,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14139,7 +14127,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14168,7 +14156,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14197,7 +14185,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14226,7 +14214,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14255,7 +14243,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14313,7 +14301,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14342,7 +14330,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14371,7 +14359,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14400,7 +14388,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14429,7 +14417,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14458,7 +14446,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14487,7 +14475,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14545,7 +14533,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14574,7 +14562,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14603,7 +14591,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14661,7 +14649,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14719,7 +14707,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14777,7 +14765,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14806,7 +14794,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14835,7 +14823,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14864,7 +14852,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14893,7 +14881,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14922,7 +14910,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14980,7 +14968,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -15009,7 +14997,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15038,7 +15026,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15067,7 +15055,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15096,7 +15084,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15125,7 +15113,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15183,7 +15171,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15212,7 +15200,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15241,7 +15229,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15270,7 +15258,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15299,7 +15287,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15328,7 +15316,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15386,7 +15374,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15415,7 +15403,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15444,7 +15432,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15473,7 +15461,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15502,7 +15490,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15531,7 +15519,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15560,7 +15548,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15589,7 +15577,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15618,7 +15606,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15647,7 +15635,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15676,7 +15664,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15705,7 +15693,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15734,7 +15722,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15763,7 +15751,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15792,7 +15780,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15821,7 +15809,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15850,7 +15838,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15908,7 +15896,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15966,7 +15954,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15995,7 +15983,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16053,7 +16041,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16111,7 +16099,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16140,7 +16128,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16169,7 +16157,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16198,7 +16186,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16256,7 +16244,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16285,7 +16273,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16314,7 +16302,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16343,7 +16331,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16372,7 +16360,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16401,7 +16389,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16430,7 +16418,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16459,7 +16447,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16488,7 +16476,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16517,7 +16505,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16546,7 +16534,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16575,7 +16563,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16604,7 +16592,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16633,7 +16621,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16662,7 +16650,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16691,7 +16679,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16778,7 +16766,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16807,7 +16795,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16836,7 +16824,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16894,7 +16882,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16923,7 +16911,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -17010,7 +16998,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17039,7 +17027,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17068,7 +17056,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17097,7 +17085,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17126,7 +17114,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17184,7 +17172,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17213,7 +17201,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17271,7 +17259,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17300,7 +17288,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17329,7 +17317,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17358,7 +17346,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17387,7 +17375,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17445,7 +17433,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17474,7 +17462,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17503,7 +17491,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17532,7 +17520,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17561,7 +17549,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17590,7 +17578,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17619,7 +17607,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17648,7 +17636,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17677,7 +17665,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17706,7 +17694,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17735,7 +17723,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17764,7 +17752,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17793,7 +17781,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17851,7 +17839,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17880,7 +17868,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17909,7 +17897,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17938,7 +17926,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17967,7 +17955,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="2" t="n">
+      <c r="A605" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17996,7 +17984,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18025,7 +18013,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="2" t="n">
+      <c r="A607" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I607"/>
+  <dimension ref="A1:I608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17988,16 +17988,16 @@
         <v>46234</v>
       </c>
       <c r="B606" t="n">
-        <v>-3548.426043</v>
+        <v>-3545.719043</v>
       </c>
       <c r="C606" t="n">
-        <v>-214.757483</v>
+        <v>-212.050483</v>
       </c>
       <c r="D606" t="n">
         <v>-3333.66856</v>
       </c>
       <c r="E606" t="n">
-        <v>-137.958</v>
+        <v>-135.251</v>
       </c>
       <c r="F606" t="n">
         <v>-76.799483</v>
@@ -18017,16 +18017,16 @@
         <v>46241</v>
       </c>
       <c r="B607" t="n">
-        <v>1770.35629</v>
+        <v>1769.54729</v>
       </c>
       <c r="C607" t="n">
-        <v>1402.625228</v>
+        <v>1401.816228</v>
       </c>
       <c r="D607" t="n">
         <v>367.731062</v>
       </c>
       <c r="E607" t="n">
-        <v>480.05</v>
+        <v>479.241</v>
       </c>
       <c r="F607" t="n">
         <v>922.575228</v>
@@ -18039,6 +18039,35 @@
       </c>
       <c r="I607" t="n">
         <v>24.76</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B608" t="n">
+        <v>-297.346712</v>
+      </c>
+      <c r="C608" t="n">
+        <v>-1056.445654</v>
+      </c>
+      <c r="D608" t="n">
+        <v>759.098942</v>
+      </c>
+      <c r="E608" t="n">
+        <v>-197.165</v>
+      </c>
+      <c r="F608" t="n">
+        <v>-859.280654</v>
+      </c>
+      <c r="G608" t="n">
+        <v>-827.169</v>
+      </c>
+      <c r="H608" t="n">
+        <v>-30.243654</v>
+      </c>
+      <c r="I608" t="n">
+        <v>-1.868</v>
       </c>
     </row>
   </sheetData>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,54 +433,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -671,7 +683,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -903,7 +915,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -932,7 +944,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1106,7 +1118,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1135,7 +1147,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1222,7 +1234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1280,7 +1292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1367,7 +1379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1715,7 +1727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1976,7 +1988,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2034,7 +2046,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2063,7 +2075,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2266,7 +2278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2527,7 +2539,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2672,7 +2684,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2701,7 +2713,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2962,7 +2974,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3107,7 +3119,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3136,7 +3148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3339,7 +3351,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3397,7 +3409,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3426,7 +3438,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3542,7 +3554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3571,7 +3583,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3629,7 +3641,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3687,7 +3699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3774,7 +3786,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3803,7 +3815,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3919,7 +3931,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3977,7 +3989,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4006,7 +4018,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4035,7 +4047,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4064,7 +4076,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4296,7 +4308,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4441,7 +4453,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4470,7 +4482,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4499,7 +4511,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4528,7 +4540,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4586,7 +4598,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4615,7 +4627,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4644,7 +4656,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4789,7 +4801,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4818,7 +4830,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4905,7 +4917,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -4992,7 +5004,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5021,7 +5033,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5050,7 +5062,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5224,7 +5236,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5253,7 +5265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5311,7 +5323,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5369,7 +5381,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5630,7 +5642,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5688,7 +5700,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6094,7 +6106,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6152,7 +6164,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6384,7 +6396,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6442,7 +6454,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6500,7 +6512,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6645,7 +6657,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6819,7 +6831,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6848,7 +6860,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7225,7 +7237,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7254,7 +7266,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7312,7 +7324,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7341,7 +7353,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7370,7 +7382,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7428,7 +7440,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7457,7 +7469,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7515,7 +7527,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7573,7 +7585,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7631,7 +7643,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7718,7 +7730,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7747,7 +7759,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7776,7 +7788,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7805,7 +7817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7834,7 +7846,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7863,7 +7875,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7892,7 +7904,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7921,7 +7933,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7979,7 +7991,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8037,7 +8049,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8095,7 +8107,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8153,7 +8165,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8182,7 +8194,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8211,7 +8223,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8240,7 +8252,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8298,7 +8310,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8327,7 +8339,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8414,7 +8426,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8443,7 +8455,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8472,7 +8484,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8501,7 +8513,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8530,7 +8542,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8617,7 +8629,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8646,7 +8658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8675,7 +8687,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8704,7 +8716,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8791,7 +8803,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8820,7 +8832,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8849,7 +8861,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8878,7 +8890,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8907,7 +8919,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -8994,7 +9006,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9023,7 +9035,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9081,7 +9093,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9168,7 +9180,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9226,7 +9238,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9255,7 +9267,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9284,7 +9296,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9313,7 +9325,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9342,7 +9354,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9371,7 +9383,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9400,7 +9412,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9429,7 +9441,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9487,7 +9499,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9545,7 +9557,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9574,7 +9586,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9603,7 +9615,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9719,7 +9731,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9777,7 +9789,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9864,7 +9876,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9893,7 +9905,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9922,7 +9934,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9951,7 +9963,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10009,7 +10021,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10067,7 +10079,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10096,7 +10108,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10125,7 +10137,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10154,7 +10166,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10212,7 +10224,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10299,7 +10311,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10357,7 +10369,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10444,7 +10456,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10531,7 +10543,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10560,7 +10572,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10589,7 +10601,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10618,7 +10630,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10647,7 +10659,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10705,7 +10717,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10763,7 +10775,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10792,7 +10804,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10821,7 +10833,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10850,7 +10862,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10879,7 +10891,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10937,7 +10949,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10966,7 +10978,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -10995,7 +11007,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11024,7 +11036,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11053,7 +11065,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11082,7 +11094,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11140,7 +11152,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11198,7 +11210,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11256,7 +11268,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11285,7 +11297,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11343,7 +11355,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11372,7 +11384,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11401,7 +11413,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11430,7 +11442,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11459,7 +11471,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11488,7 +11500,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11546,7 +11558,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11575,7 +11587,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11604,7 +11616,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11691,7 +11703,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11720,7 +11732,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11749,7 +11761,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11807,7 +11819,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11865,7 +11877,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11894,7 +11906,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11952,7 +11964,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11981,7 +11993,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12039,7 +12051,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12068,7 +12080,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12097,7 +12109,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12126,7 +12138,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12213,7 +12225,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12242,7 +12254,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12271,7 +12283,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12300,7 +12312,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12329,7 +12341,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12416,7 +12428,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12445,7 +12457,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12474,7 +12486,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12503,7 +12515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12532,7 +12544,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12561,7 +12573,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12619,7 +12631,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12648,7 +12660,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12677,7 +12689,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12735,7 +12747,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12764,7 +12776,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12822,7 +12834,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12851,7 +12863,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12880,7 +12892,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12909,7 +12921,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12938,7 +12950,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12967,7 +12979,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -12996,7 +13008,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13025,7 +13037,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13054,7 +13066,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13112,7 +13124,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13199,7 +13211,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13228,7 +13240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13257,7 +13269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13286,7 +13298,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13344,7 +13356,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13373,7 +13385,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13402,7 +13414,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13431,7 +13443,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13518,7 +13530,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13576,7 +13588,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13605,7 +13617,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13634,7 +13646,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13692,7 +13704,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13721,7 +13733,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13750,7 +13762,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13837,7 +13849,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13924,7 +13936,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13953,7 +13965,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13982,7 +13994,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14040,7 +14052,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14098,7 +14110,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14127,7 +14139,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14156,7 +14168,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14185,7 +14197,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14214,7 +14226,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14272,7 +14284,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14301,7 +14313,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14330,7 +14342,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14359,7 +14371,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14388,7 +14400,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14417,7 +14429,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14446,7 +14458,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14475,7 +14487,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14562,7 +14574,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14591,7 +14603,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14649,7 +14661,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14678,7 +14690,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14707,7 +14719,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14765,7 +14777,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14794,7 +14806,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14823,7 +14835,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14852,7 +14864,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14881,7 +14893,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14910,7 +14922,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14968,7 +14980,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -14997,7 +15009,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15026,7 +15038,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15055,7 +15067,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15171,7 +15183,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15200,7 +15212,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15229,7 +15241,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15287,7 +15299,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15316,7 +15328,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15374,7 +15386,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15403,7 +15415,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15432,7 +15444,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15461,7 +15473,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15490,7 +15502,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15519,7 +15531,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15548,7 +15560,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15577,7 +15589,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15606,7 +15618,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15635,7 +15647,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15664,7 +15676,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15693,7 +15705,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15722,7 +15734,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15751,7 +15763,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15780,7 +15792,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15809,7 +15821,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15838,7 +15850,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15896,7 +15908,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15925,7 +15937,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15954,7 +15966,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15983,7 +15995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16041,7 +16053,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16099,7 +16111,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16128,7 +16140,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16157,7 +16169,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16186,7 +16198,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16244,7 +16256,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16302,7 +16314,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16331,7 +16343,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16360,7 +16372,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16389,7 +16401,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16418,7 +16430,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16447,7 +16459,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16476,7 +16488,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16505,7 +16517,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16534,7 +16546,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16563,7 +16575,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16592,7 +16604,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16621,7 +16633,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16650,7 +16662,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16679,7 +16691,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16708,7 +16720,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16766,7 +16778,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16795,7 +16807,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16824,7 +16836,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16853,7 +16865,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16882,7 +16894,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16911,7 +16923,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16969,7 +16981,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -16998,7 +17010,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17027,7 +17039,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17056,7 +17068,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17085,7 +17097,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17172,7 +17184,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17201,7 +17213,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17288,7 +17300,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17317,7 +17329,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17346,7 +17358,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17375,7 +17387,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17433,7 +17445,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17491,7 +17503,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17520,7 +17532,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17549,7 +17561,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17578,7 +17590,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17607,7 +17619,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17636,7 +17648,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17665,7 +17677,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17723,7 +17735,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17752,7 +17764,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17781,7 +17793,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17839,7 +17851,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17868,7 +17880,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17897,7 +17909,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17926,7 +17938,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17955,7 +17967,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17984,7 +17996,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18013,7 +18025,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">
@@ -18042,7 +18054,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B608" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,58 +417,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I608"/>
+  <dimension ref="A1:I609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -567,7 +555,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -596,7 +584,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -625,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -683,7 +671,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -712,7 +700,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -828,7 +816,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -944,7 +932,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +990,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1089,7 +1077,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1118,7 +1106,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1147,7 +1135,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1292,7 +1280,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1350,7 +1338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1379,7 +1367,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1408,7 +1396,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1553,7 +1541,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1582,7 +1570,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1611,7 +1599,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1640,7 +1628,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1669,7 +1657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1727,7 +1715,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1814,7 +1802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1843,7 +1831,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1872,7 +1860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1959,7 +1947,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1988,7 +1976,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2046,7 +2034,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2075,7 +2063,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2104,7 +2092,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2133,7 +2121,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2162,7 +2150,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2191,7 +2179,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2307,7 +2295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2336,7 +2324,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2365,7 +2353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2423,7 +2411,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2452,7 +2440,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2568,7 +2556,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2597,7 +2585,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2684,7 +2672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2713,7 +2701,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2771,7 +2759,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2800,7 +2788,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2887,7 +2875,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2945,7 +2933,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2974,7 +2962,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3032,7 +3020,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3061,7 +3049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3090,7 +3078,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3119,7 +3107,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3148,7 +3136,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3177,7 +3165,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3206,7 +3194,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3264,7 +3252,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3380,7 +3368,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3496,7 +3484,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3525,7 +3513,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3554,7 +3542,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3583,7 +3571,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3641,7 +3629,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3670,7 +3658,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3699,7 +3687,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3757,7 +3745,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3786,7 +3774,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3815,7 +3803,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3844,7 +3832,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3873,7 +3861,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3902,7 +3890,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3931,7 +3919,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3989,7 +3977,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4047,7 +4035,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4076,7 +4064,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4163,7 +4151,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4250,7 +4238,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4279,7 +4267,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4337,7 +4325,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4366,7 +4354,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4395,7 +4383,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4424,7 +4412,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4453,7 +4441,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4482,7 +4470,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4511,7 +4499,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4540,7 +4528,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4627,7 +4615,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4656,7 +4644,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4685,7 +4673,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4743,7 +4731,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4772,7 +4760,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4801,7 +4789,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4830,7 +4818,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4859,7 +4847,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4888,7 +4876,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4917,7 +4905,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -5004,7 +4992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5033,7 +5021,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5062,7 +5050,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5091,7 +5079,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5120,7 +5108,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5178,7 +5166,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5207,7 +5195,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5236,7 +5224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5294,7 +5282,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5323,7 +5311,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5352,7 +5340,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5410,7 +5398,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5439,7 +5427,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5468,7 +5456,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5497,7 +5485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5526,7 +5514,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5584,7 +5572,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5613,7 +5601,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5642,7 +5630,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5671,7 +5659,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5729,7 +5717,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5787,7 +5775,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5874,7 +5862,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5903,7 +5891,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5990,7 +5978,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6048,7 +6036,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6077,7 +6065,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6106,7 +6094,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6135,7 +6123,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6164,7 +6152,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6193,7 +6181,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6251,7 +6239,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6280,7 +6268,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6309,7 +6297,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6367,7 +6355,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6396,7 +6384,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6454,7 +6442,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6483,7 +6471,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6512,7 +6500,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6570,7 +6558,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6599,7 +6587,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6628,7 +6616,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6657,7 +6645,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6686,7 +6674,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6715,7 +6703,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6744,7 +6732,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6773,7 +6761,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6802,7 +6790,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6831,7 +6819,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6860,7 +6848,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6947,7 +6935,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6976,7 +6964,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -7005,7 +6993,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7034,7 +7022,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7063,7 +7051,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7150,7 +7138,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7237,7 +7225,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7266,7 +7254,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7324,7 +7312,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7353,7 +7341,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7382,7 +7370,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7411,7 +7399,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7440,7 +7428,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7469,7 +7457,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7527,7 +7515,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7585,7 +7573,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7614,7 +7602,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7643,7 +7631,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7672,7 +7660,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7730,7 +7718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7759,7 +7747,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7788,7 +7776,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7846,7 +7834,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7875,7 +7863,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7904,7 +7892,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7962,7 +7950,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7991,7 +7979,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8020,7 +8008,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8049,7 +8037,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8078,7 +8066,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8107,7 +8095,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8165,7 +8153,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8194,7 +8182,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8223,7 +8211,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8252,7 +8240,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8310,7 +8298,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8339,7 +8327,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8426,7 +8414,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8484,7 +8472,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8513,7 +8501,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8542,7 +8530,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8600,7 +8588,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8629,7 +8617,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8658,7 +8646,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8687,7 +8675,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8716,7 +8704,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8745,7 +8733,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8803,7 +8791,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8832,7 +8820,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8861,7 +8849,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8890,7 +8878,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8919,7 +8907,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -9006,7 +8994,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9035,7 +9023,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9122,7 +9110,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9151,7 +9139,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9180,7 +9168,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9209,7 +9197,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9238,7 +9226,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9267,7 +9255,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9296,7 +9284,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9325,7 +9313,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9354,7 +9342,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9383,7 +9371,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9412,7 +9400,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9441,7 +9429,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9470,7 +9458,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9499,7 +9487,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9528,7 +9516,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9557,7 +9545,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9586,7 +9574,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9615,7 +9603,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9731,7 +9719,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9760,7 +9748,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9789,7 +9777,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9818,7 +9806,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9876,7 +9864,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9905,7 +9893,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9934,7 +9922,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9963,7 +9951,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9992,7 +9980,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10021,7 +10009,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10079,7 +10067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10108,7 +10096,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10137,7 +10125,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10195,7 +10183,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10224,7 +10212,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10282,7 +10270,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10311,7 +10299,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10369,7 +10357,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10456,7 +10444,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10485,7 +10473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10514,7 +10502,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10543,7 +10531,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10572,7 +10560,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10630,7 +10618,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10659,7 +10647,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10688,7 +10676,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10717,7 +10705,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10746,7 +10734,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10775,7 +10763,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10804,7 +10792,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10833,7 +10821,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10862,7 +10850,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10891,7 +10879,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10978,7 +10966,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11036,7 +11024,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11065,7 +11053,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11094,7 +11082,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11152,7 +11140,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11181,7 +11169,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11210,7 +11198,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11239,7 +11227,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11268,7 +11256,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11297,7 +11285,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11355,7 +11343,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11384,7 +11372,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11413,7 +11401,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11442,7 +11430,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11471,7 +11459,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11500,7 +11488,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11558,7 +11546,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11587,7 +11575,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11616,7 +11604,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11645,7 +11633,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11674,7 +11662,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11703,7 +11691,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11732,7 +11720,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11761,7 +11749,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11877,7 +11865,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11906,7 +11894,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11935,7 +11923,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11993,7 +11981,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12022,7 +12010,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12051,7 +12039,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12080,7 +12068,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12109,7 +12097,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12138,7 +12126,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12167,7 +12155,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12225,7 +12213,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12254,7 +12242,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12283,7 +12271,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12312,7 +12300,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12341,7 +12329,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12370,7 +12358,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12428,7 +12416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12457,7 +12445,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12486,7 +12474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12515,7 +12503,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12573,7 +12561,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12631,7 +12619,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12660,7 +12648,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12689,7 +12677,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12718,7 +12706,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12747,7 +12735,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12776,7 +12764,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12834,7 +12822,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12863,7 +12851,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12892,7 +12880,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12921,7 +12909,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12950,7 +12938,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12979,7 +12967,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -13008,7 +12996,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13037,7 +13025,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13066,7 +13054,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13095,7 +13083,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13240,7 +13228,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13269,7 +13257,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13298,7 +13286,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13327,7 +13315,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13356,7 +13344,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13385,7 +13373,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13414,7 +13402,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13501,7 +13489,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13530,7 +13518,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13559,7 +13547,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13588,7 +13576,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13617,7 +13605,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13646,7 +13634,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13704,7 +13692,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13733,7 +13721,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13762,7 +13750,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13820,7 +13808,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13849,7 +13837,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13907,7 +13895,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13936,7 +13924,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13965,7 +13953,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13994,7 +13982,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14023,7 +14011,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14052,7 +14040,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14110,7 +14098,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14139,7 +14127,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14168,7 +14156,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14197,7 +14185,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14226,7 +14214,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14255,7 +14243,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14313,7 +14301,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14342,7 +14330,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14371,7 +14359,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14400,7 +14388,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14429,7 +14417,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14458,7 +14446,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14487,7 +14475,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14545,7 +14533,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14574,7 +14562,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14603,7 +14591,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14661,7 +14649,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14719,7 +14707,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14777,7 +14765,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14806,7 +14794,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14835,7 +14823,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14864,7 +14852,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14893,7 +14881,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14922,7 +14910,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14980,7 +14968,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -15009,7 +14997,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15038,7 +15026,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15067,7 +15055,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15096,7 +15084,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15125,7 +15113,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15183,7 +15171,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15212,7 +15200,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15241,7 +15229,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15270,7 +15258,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15299,7 +15287,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15328,7 +15316,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15386,7 +15374,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15415,7 +15403,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15444,7 +15432,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15473,7 +15461,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15502,7 +15490,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15531,7 +15519,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15560,7 +15548,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15589,7 +15577,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15618,7 +15606,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15647,7 +15635,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15676,7 +15664,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15705,7 +15693,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15734,7 +15722,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15763,7 +15751,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15792,7 +15780,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15821,7 +15809,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15850,7 +15838,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15908,7 +15896,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15966,7 +15954,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15995,7 +15983,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16053,7 +16041,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16111,7 +16099,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16140,7 +16128,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16169,7 +16157,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16198,7 +16186,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16256,7 +16244,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16285,7 +16273,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16314,7 +16302,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16343,7 +16331,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16372,7 +16360,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16401,7 +16389,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16430,7 +16418,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16459,7 +16447,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16488,7 +16476,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16517,7 +16505,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16546,7 +16534,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16575,7 +16563,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16604,7 +16592,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16633,7 +16621,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16662,7 +16650,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16691,7 +16679,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16778,7 +16766,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16807,7 +16795,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16836,7 +16824,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16894,7 +16882,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16923,7 +16911,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -17010,7 +16998,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17039,7 +17027,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17068,7 +17056,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17097,7 +17085,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17126,7 +17114,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17184,7 +17172,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17213,7 +17201,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17271,7 +17259,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17300,7 +17288,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17329,7 +17317,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17358,7 +17346,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17387,7 +17375,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17445,7 +17433,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17474,7 +17462,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17503,7 +17491,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17532,7 +17520,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17561,7 +17549,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17590,7 +17578,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17619,7 +17607,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17648,7 +17636,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17677,7 +17665,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17706,7 +17694,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17735,7 +17723,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17764,7 +17752,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17793,7 +17781,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17851,7 +17839,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17880,7 +17868,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17909,7 +17897,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17938,7 +17926,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17967,7 +17955,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="2" t="n">
+      <c r="A605" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17996,7 +17984,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18025,7 +18013,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="2" t="n">
+      <c r="A607" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">
@@ -18054,7 +18042,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="2" t="n">
+      <c r="A608" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B608" t="n">
@@ -18080,6 +18068,35 @@
       </c>
       <c r="I608" t="n">
         <v>-1.868</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B609" t="n">
+        <v>1135.744708</v>
+      </c>
+      <c r="C609" t="n">
+        <v>774.704442</v>
+      </c>
+      <c r="D609" t="n">
+        <v>361.040266</v>
+      </c>
+      <c r="E609" t="n">
+        <v>189.926</v>
+      </c>
+      <c r="F609" t="n">
+        <v>584.778442</v>
+      </c>
+      <c r="G609" t="n">
+        <v>315.702</v>
+      </c>
+      <c r="H609" t="n">
+        <v>244.428442</v>
+      </c>
+      <c r="I609" t="n">
+        <v>24.648</v>
       </c>
     </row>
   </sheetData>

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,54 +433,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -497,7 +509,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -555,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -584,7 +596,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -613,7 +625,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -642,7 +654,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -671,7 +683,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -700,7 +712,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -729,7 +741,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -758,7 +770,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -874,7 +886,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -903,7 +915,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -932,7 +944,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -961,7 +973,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -990,7 +1002,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1048,7 +1060,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1077,7 +1089,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1106,7 +1118,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1135,7 +1147,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1193,7 +1205,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1222,7 +1234,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1251,7 +1263,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1280,7 +1292,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1309,7 +1321,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1338,7 +1350,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1367,7 +1379,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1396,7 +1408,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1425,7 +1437,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1454,7 +1466,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1512,7 +1524,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1541,7 +1553,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1570,7 +1582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1628,7 +1640,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1657,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1686,7 +1698,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1715,7 +1727,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1744,7 +1756,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1773,7 +1785,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1831,7 +1843,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1860,7 +1872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1918,7 +1930,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1947,7 +1959,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1976,7 +1988,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2034,7 +2046,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2063,7 +2075,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2092,7 +2104,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2150,7 +2162,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2179,7 +2191,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2208,7 +2220,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2237,7 +2249,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2266,7 +2278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2295,7 +2307,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2324,7 +2336,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2353,7 +2365,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2382,7 +2394,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2411,7 +2423,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2469,7 +2481,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2498,7 +2510,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2527,7 +2539,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2556,7 +2568,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2585,7 +2597,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2672,7 +2684,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2701,7 +2713,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2730,7 +2742,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2788,7 +2800,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2817,7 +2829,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2846,7 +2858,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2875,7 +2887,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2904,7 +2916,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2933,7 +2945,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2962,7 +2974,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3020,7 +3032,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3049,7 +3061,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3107,7 +3119,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3136,7 +3148,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3165,7 +3177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3223,7 +3235,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3252,7 +3264,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3310,7 +3322,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3339,7 +3351,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3368,7 +3380,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3397,7 +3409,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3426,7 +3438,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3455,7 +3467,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3484,7 +3496,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3513,7 +3525,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3542,7 +3554,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3571,7 +3583,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3600,7 +3612,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3629,7 +3641,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3658,7 +3670,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3687,7 +3699,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3716,7 +3728,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3745,7 +3757,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3774,7 +3786,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3803,7 +3815,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3832,7 +3844,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3890,7 +3902,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3919,7 +3931,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3948,7 +3960,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3977,7 +3989,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4006,7 +4018,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4035,7 +4047,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4064,7 +4076,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4151,7 +4163,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4180,7 +4192,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4209,7 +4221,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4238,7 +4250,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4267,7 +4279,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4296,7 +4308,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4325,7 +4337,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4354,7 +4366,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4412,7 +4424,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4441,7 +4453,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4470,7 +4482,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4499,7 +4511,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4528,7 +4540,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4586,7 +4598,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4615,7 +4627,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4644,7 +4656,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4673,7 +4685,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4702,7 +4714,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4731,7 +4743,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4760,7 +4772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4789,7 +4801,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4818,7 +4830,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4847,7 +4859,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4876,7 +4888,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4905,7 +4917,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4934,7 +4946,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4963,7 +4975,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -4992,7 +5004,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5021,7 +5033,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5050,7 +5062,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5079,7 +5091,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5108,7 +5120,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5137,7 +5149,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5195,7 +5207,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5224,7 +5236,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5253,7 +5265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5282,7 +5294,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5311,7 +5323,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5340,7 +5352,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5369,7 +5381,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5398,7 +5410,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5427,7 +5439,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5456,7 +5468,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5485,7 +5497,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5514,7 +5526,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5543,7 +5555,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5601,7 +5613,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5630,7 +5642,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5659,7 +5671,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5688,7 +5700,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5717,7 +5729,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5746,7 +5758,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5775,7 +5787,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5804,7 +5816,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5862,7 +5874,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5891,7 +5903,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5920,7 +5932,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5949,7 +5961,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5978,7 +5990,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6007,7 +6019,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6036,7 +6048,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6065,7 +6077,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6094,7 +6106,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6123,7 +6135,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6152,7 +6164,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6181,7 +6193,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6210,7 +6222,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6239,7 +6251,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6268,7 +6280,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6297,7 +6309,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6326,7 +6338,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6355,7 +6367,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6384,7 +6396,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6413,7 +6425,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6442,7 +6454,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6471,7 +6483,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6500,7 +6512,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6529,7 +6541,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6558,7 +6570,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6587,7 +6599,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6616,7 +6628,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6645,7 +6657,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6674,7 +6686,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6703,7 +6715,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6732,7 +6744,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6790,7 +6802,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6819,7 +6831,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6848,7 +6860,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6877,7 +6889,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6906,7 +6918,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6935,7 +6947,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6964,7 +6976,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -6993,7 +7005,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7022,7 +7034,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7051,7 +7063,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7080,7 +7092,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7138,7 +7150,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7167,7 +7179,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7196,7 +7208,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7225,7 +7237,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7254,7 +7266,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7283,7 +7295,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7312,7 +7324,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7341,7 +7353,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7370,7 +7382,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7399,7 +7411,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7428,7 +7440,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7457,7 +7469,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7486,7 +7498,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7515,7 +7527,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7573,7 +7585,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7602,7 +7614,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7631,7 +7643,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7660,7 +7672,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7689,7 +7701,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7718,7 +7730,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7747,7 +7759,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7776,7 +7788,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7805,7 +7817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7834,7 +7846,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7863,7 +7875,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7892,7 +7904,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7921,7 +7933,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7979,7 +7991,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8008,7 +8020,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8037,7 +8049,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8066,7 +8078,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8095,7 +8107,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8124,7 +8136,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8153,7 +8165,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8182,7 +8194,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8211,7 +8223,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8240,7 +8252,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8269,7 +8281,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8298,7 +8310,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8327,7 +8339,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8356,7 +8368,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8414,7 +8426,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8443,7 +8455,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8472,7 +8484,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8501,7 +8513,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8530,7 +8542,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8559,7 +8571,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8588,7 +8600,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8617,7 +8629,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8646,7 +8658,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8675,7 +8687,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8704,7 +8716,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8733,7 +8745,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8762,7 +8774,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8791,7 +8803,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8820,7 +8832,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8849,7 +8861,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8878,7 +8890,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8907,7 +8919,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8936,7 +8948,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8965,7 +8977,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -8994,7 +9006,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9023,7 +9035,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9052,7 +9064,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9081,7 +9093,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9110,7 +9122,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9168,7 +9180,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9197,7 +9209,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9226,7 +9238,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9255,7 +9267,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9284,7 +9296,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9313,7 +9325,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9342,7 +9354,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9371,7 +9383,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9400,7 +9412,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9429,7 +9441,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9458,7 +9470,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9487,7 +9499,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9516,7 +9528,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9545,7 +9557,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9574,7 +9586,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9603,7 +9615,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9632,7 +9644,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9690,7 +9702,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9719,7 +9731,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9748,7 +9760,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9777,7 +9789,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9806,7 +9818,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9835,7 +9847,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9864,7 +9876,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9893,7 +9905,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9922,7 +9934,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9951,7 +9963,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9980,7 +9992,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10009,7 +10021,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10038,7 +10050,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10067,7 +10079,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10096,7 +10108,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10125,7 +10137,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10154,7 +10166,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10183,7 +10195,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10212,7 +10224,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10241,7 +10253,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10270,7 +10282,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10299,7 +10311,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10357,7 +10369,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10415,7 +10427,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10444,7 +10456,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10473,7 +10485,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10502,7 +10514,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10531,7 +10543,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10560,7 +10572,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10589,7 +10601,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10618,7 +10630,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10647,7 +10659,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10676,7 +10688,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10705,7 +10717,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10734,7 +10746,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10763,7 +10775,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10792,7 +10804,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10821,7 +10833,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10850,7 +10862,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10879,7 +10891,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10908,7 +10920,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10937,7 +10949,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10966,7 +10978,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -10995,7 +11007,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11024,7 +11036,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11053,7 +11065,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11082,7 +11094,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11111,7 +11123,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11140,7 +11152,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11169,7 +11181,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11198,7 +11210,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11227,7 +11239,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11256,7 +11268,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11285,7 +11297,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11314,7 +11326,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11343,7 +11355,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11372,7 +11384,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11401,7 +11413,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11430,7 +11442,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11459,7 +11471,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11488,7 +11500,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11546,7 +11558,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11575,7 +11587,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11604,7 +11616,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11633,7 +11645,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11662,7 +11674,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11691,7 +11703,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11720,7 +11732,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11749,7 +11761,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11778,7 +11790,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11807,7 +11819,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11865,7 +11877,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11894,7 +11906,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11923,7 +11935,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11952,7 +11964,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11981,7 +11993,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12010,7 +12022,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12039,7 +12051,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12068,7 +12080,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12097,7 +12109,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12126,7 +12138,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12155,7 +12167,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12184,7 +12196,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12213,7 +12225,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12242,7 +12254,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12271,7 +12283,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12300,7 +12312,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12329,7 +12341,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12358,7 +12370,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12387,7 +12399,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12416,7 +12428,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12445,7 +12457,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12474,7 +12486,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12503,7 +12515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12532,7 +12544,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12561,7 +12573,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12590,7 +12602,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12619,7 +12631,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12648,7 +12660,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12677,7 +12689,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12735,7 +12747,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12764,7 +12776,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12793,7 +12805,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12822,7 +12834,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12851,7 +12863,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12880,7 +12892,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12909,7 +12921,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12938,7 +12950,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12967,7 +12979,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -12996,7 +13008,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13025,7 +13037,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13054,7 +13066,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13083,7 +13095,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13112,7 +13124,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13141,7 +13153,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13199,7 +13211,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13228,7 +13240,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13257,7 +13269,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13286,7 +13298,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13315,7 +13327,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13344,7 +13356,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13373,7 +13385,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13402,7 +13414,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13431,7 +13443,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13460,7 +13472,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13489,7 +13501,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13518,7 +13530,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13547,7 +13559,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13576,7 +13588,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13605,7 +13617,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13634,7 +13646,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13663,7 +13675,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13692,7 +13704,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13721,7 +13733,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13750,7 +13762,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13779,7 +13791,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13808,7 +13820,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13837,7 +13849,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13866,7 +13878,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13924,7 +13936,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13953,7 +13965,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13982,7 +13994,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14011,7 +14023,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14040,7 +14052,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14069,7 +14081,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14098,7 +14110,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14127,7 +14139,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14156,7 +14168,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14185,7 +14197,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14214,7 +14226,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14243,7 +14255,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14272,7 +14284,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14301,7 +14313,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14330,7 +14342,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14359,7 +14371,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14388,7 +14400,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14417,7 +14429,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14446,7 +14458,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14475,7 +14487,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14504,7 +14516,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14533,7 +14545,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14562,7 +14574,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14591,7 +14603,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14649,7 +14661,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14678,7 +14690,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14707,7 +14719,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14736,7 +14748,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14765,7 +14777,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14794,7 +14806,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14823,7 +14835,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14852,7 +14864,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14881,7 +14893,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14910,7 +14922,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14939,7 +14951,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14968,7 +14980,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -14997,7 +15009,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15026,7 +15038,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15055,7 +15067,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15113,7 +15125,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15142,7 +15154,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15171,7 +15183,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15200,7 +15212,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15229,7 +15241,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15258,7 +15270,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15287,7 +15299,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15316,7 +15328,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15345,7 +15357,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15374,7 +15386,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15403,7 +15415,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15432,7 +15444,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15461,7 +15473,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15490,7 +15502,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15519,7 +15531,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15548,7 +15560,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15577,7 +15589,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15606,7 +15618,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15635,7 +15647,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15664,7 +15676,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15693,7 +15705,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15722,7 +15734,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15751,7 +15763,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15780,7 +15792,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15809,7 +15821,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15838,7 +15850,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15867,7 +15879,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15896,7 +15908,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15925,7 +15937,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15954,7 +15966,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15983,7 +15995,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16012,7 +16024,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16041,7 +16053,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16099,7 +16111,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16128,7 +16140,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16157,7 +16169,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16186,7 +16198,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16215,7 +16227,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16244,7 +16256,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16302,7 +16314,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16331,7 +16343,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16360,7 +16372,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16389,7 +16401,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16418,7 +16430,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16447,7 +16459,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16476,7 +16488,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16505,7 +16517,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16534,7 +16546,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16563,7 +16575,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16592,7 +16604,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16621,7 +16633,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16650,7 +16662,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16679,7 +16691,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16708,7 +16720,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16737,7 +16749,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16766,7 +16778,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16795,7 +16807,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16824,7 +16836,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16853,7 +16865,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16882,7 +16894,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16911,7 +16923,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16940,7 +16952,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16969,7 +16981,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -16998,7 +17010,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17027,7 +17039,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17056,7 +17068,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17085,7 +17097,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17114,7 +17126,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17143,7 +17155,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17172,7 +17184,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17201,7 +17213,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17230,7 +17242,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17259,7 +17271,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17288,7 +17300,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17317,7 +17329,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17346,7 +17358,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17375,7 +17387,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17433,7 +17445,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17491,7 +17503,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17520,7 +17532,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17549,7 +17561,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17578,7 +17590,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17607,7 +17619,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17636,7 +17648,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17665,7 +17677,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17694,7 +17706,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17723,7 +17735,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17752,7 +17764,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17781,7 +17793,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17810,7 +17822,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17839,7 +17851,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17868,7 +17880,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17897,7 +17909,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17926,7 +17938,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17955,7 +17967,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17984,7 +17996,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18013,7 +18025,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">
@@ -18042,7 +18054,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="B608" t="n">
@@ -18071,7 +18083,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>46255</v>
       </c>
       <c r="B609" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Haftalik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,54 +421,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yerlesik_toplam</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>gercek_kisiler</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>tuzel_kisiler</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gk_altin</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>gk_doviz</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>gk_usd</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gk_eur</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>gk_diger</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42006</v>
       </c>
       <c r="B2" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42013</v>
       </c>
       <c r="B3" t="n">
@@ -538,7 +526,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42020</v>
       </c>
       <c r="B4" t="n">
@@ -567,7 +555,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42027</v>
       </c>
       <c r="B5" t="n">
@@ -596,7 +584,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42034</v>
       </c>
       <c r="B6" t="n">
@@ -625,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="B7" t="n">
@@ -654,7 +642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42048</v>
       </c>
       <c r="B8" t="n">
@@ -683,7 +671,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42055</v>
       </c>
       <c r="B9" t="n">
@@ -712,7 +700,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42062</v>
       </c>
       <c r="B10" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="B11" t="n">
@@ -770,7 +758,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42076</v>
       </c>
       <c r="B12" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42083</v>
       </c>
       <c r="B13" t="n">
@@ -828,7 +816,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42090</v>
       </c>
       <c r="B14" t="n">
@@ -857,7 +845,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42097</v>
       </c>
       <c r="B15" t="n">
@@ -886,7 +874,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42104</v>
       </c>
       <c r="B16" t="n">
@@ -915,7 +903,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42111</v>
       </c>
       <c r="B17" t="n">
@@ -944,7 +932,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42118</v>
       </c>
       <c r="B18" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B19" t="n">
@@ -1002,7 +990,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42132</v>
       </c>
       <c r="B20" t="n">
@@ -1031,7 +1019,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42139</v>
       </c>
       <c r="B21" t="n">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42146</v>
       </c>
       <c r="B22" t="n">
@@ -1089,7 +1077,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>42153</v>
       </c>
       <c r="B23" t="n">
@@ -1118,7 +1106,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>42160</v>
       </c>
       <c r="B24" t="n">
@@ -1147,7 +1135,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>42167</v>
       </c>
       <c r="B25" t="n">
@@ -1176,7 +1164,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>42174</v>
       </c>
       <c r="B26" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>42181</v>
       </c>
       <c r="B27" t="n">
@@ -1234,7 +1222,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>42188</v>
       </c>
       <c r="B28" t="n">
@@ -1263,7 +1251,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="B29" t="n">
@@ -1292,7 +1280,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>42202</v>
       </c>
       <c r="B30" t="n">
@@ -1321,7 +1309,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>42209</v>
       </c>
       <c r="B31" t="n">
@@ -1350,7 +1338,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B32" t="n">
@@ -1379,7 +1367,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>42223</v>
       </c>
       <c r="B33" t="n">
@@ -1408,7 +1396,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>42230</v>
       </c>
       <c r="B34" t="n">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>42237</v>
       </c>
       <c r="B35" t="n">
@@ -1466,7 +1454,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>42244</v>
       </c>
       <c r="B36" t="n">
@@ -1495,7 +1483,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>42251</v>
       </c>
       <c r="B37" t="n">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>42258</v>
       </c>
       <c r="B38" t="n">
@@ -1553,7 +1541,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>42265</v>
       </c>
       <c r="B39" t="n">
@@ -1582,7 +1570,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>42272</v>
       </c>
       <c r="B40" t="n">
@@ -1611,7 +1599,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>42279</v>
       </c>
       <c r="B41" t="n">
@@ -1640,7 +1628,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>42286</v>
       </c>
       <c r="B42" t="n">
@@ -1669,7 +1657,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>42293</v>
       </c>
       <c r="B43" t="n">
@@ -1698,7 +1686,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>42300</v>
       </c>
       <c r="B44" t="n">
@@ -1727,7 +1715,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>42307</v>
       </c>
       <c r="B45" t="n">
@@ -1756,7 +1744,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>42314</v>
       </c>
       <c r="B46" t="n">
@@ -1785,7 +1773,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>42321</v>
       </c>
       <c r="B47" t="n">
@@ -1814,7 +1802,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>42328</v>
       </c>
       <c r="B48" t="n">
@@ -1843,7 +1831,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>42335</v>
       </c>
       <c r="B49" t="n">
@@ -1872,7 +1860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>42342</v>
       </c>
       <c r="B50" t="n">
@@ -1901,7 +1889,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>42349</v>
       </c>
       <c r="B51" t="n">
@@ -1930,7 +1918,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>42356</v>
       </c>
       <c r="B52" t="n">
@@ -1959,7 +1947,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>42363</v>
       </c>
       <c r="B53" t="n">
@@ -1988,7 +1976,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B54" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>42377</v>
       </c>
       <c r="B55" t="n">
@@ -2046,7 +2034,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>42384</v>
       </c>
       <c r="B56" t="n">
@@ -2075,7 +2063,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>42391</v>
       </c>
       <c r="B57" t="n">
@@ -2104,7 +2092,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>42398</v>
       </c>
       <c r="B58" t="n">
@@ -2133,7 +2121,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="B59" t="n">
@@ -2162,7 +2150,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="B60" t="n">
@@ -2191,7 +2179,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>42419</v>
       </c>
       <c r="B61" t="n">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>42426</v>
       </c>
       <c r="B62" t="n">
@@ -2249,7 +2237,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>42433</v>
       </c>
       <c r="B63" t="n">
@@ -2278,7 +2266,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>42440</v>
       </c>
       <c r="B64" t="n">
@@ -2307,7 +2295,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>42447</v>
       </c>
       <c r="B65" t="n">
@@ -2336,7 +2324,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>42454</v>
       </c>
       <c r="B66" t="n">
@@ -2365,7 +2353,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B67" t="n">
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>42468</v>
       </c>
       <c r="B68" t="n">
@@ -2423,7 +2411,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>42475</v>
       </c>
       <c r="B69" t="n">
@@ -2452,7 +2440,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>42482</v>
       </c>
       <c r="B70" t="n">
@@ -2481,7 +2469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>42489</v>
       </c>
       <c r="B71" t="n">
@@ -2510,7 +2498,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>42496</v>
       </c>
       <c r="B72" t="n">
@@ -2539,7 +2527,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>42503</v>
       </c>
       <c r="B73" t="n">
@@ -2568,7 +2556,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="B74" t="n">
@@ -2597,7 +2585,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>42517</v>
       </c>
       <c r="B75" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>42524</v>
       </c>
       <c r="B76" t="n">
@@ -2655,7 +2643,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>42531</v>
       </c>
       <c r="B77" t="n">
@@ -2684,7 +2672,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>42538</v>
       </c>
       <c r="B78" t="n">
@@ -2713,7 +2701,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>42545</v>
       </c>
       <c r="B79" t="n">
@@ -2742,7 +2730,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B80" t="n">
@@ -2771,7 +2759,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>42559</v>
       </c>
       <c r="B81" t="n">
@@ -2800,7 +2788,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>42566</v>
       </c>
       <c r="B82" t="n">
@@ -2829,7 +2817,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>42573</v>
       </c>
       <c r="B83" t="n">
@@ -2858,7 +2846,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>42580</v>
       </c>
       <c r="B84" t="n">
@@ -2887,7 +2875,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>42587</v>
       </c>
       <c r="B85" t="n">
@@ -2916,7 +2904,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>42594</v>
       </c>
       <c r="B86" t="n">
@@ -2945,7 +2933,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>42601</v>
       </c>
       <c r="B87" t="n">
@@ -2974,7 +2962,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>42608</v>
       </c>
       <c r="B88" t="n">
@@ -3003,7 +2991,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>42615</v>
       </c>
       <c r="B89" t="n">
@@ -3032,7 +3020,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>42622</v>
       </c>
       <c r="B90" t="n">
@@ -3061,7 +3049,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>42629</v>
       </c>
       <c r="B91" t="n">
@@ -3090,7 +3078,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>42636</v>
       </c>
       <c r="B92" t="n">
@@ -3119,7 +3107,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B93" t="n">
@@ -3148,7 +3136,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>42650</v>
       </c>
       <c r="B94" t="n">
@@ -3177,7 +3165,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>42657</v>
       </c>
       <c r="B95" t="n">
@@ -3206,7 +3194,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>42664</v>
       </c>
       <c r="B96" t="n">
@@ -3235,7 +3223,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>42671</v>
       </c>
       <c r="B97" t="n">
@@ -3264,7 +3252,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>42678</v>
       </c>
       <c r="B98" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>42685</v>
       </c>
       <c r="B99" t="n">
@@ -3322,7 +3310,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>42692</v>
       </c>
       <c r="B100" t="n">
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>42699</v>
       </c>
       <c r="B101" t="n">
@@ -3380,7 +3368,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>42706</v>
       </c>
       <c r="B102" t="n">
@@ -3409,7 +3397,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>42713</v>
       </c>
       <c r="B103" t="n">
@@ -3438,7 +3426,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>42720</v>
       </c>
       <c r="B104" t="n">
@@ -3467,7 +3455,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>42727</v>
       </c>
       <c r="B105" t="n">
@@ -3496,7 +3484,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>42734</v>
       </c>
       <c r="B106" t="n">
@@ -3525,7 +3513,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>42741</v>
       </c>
       <c r="B107" t="n">
@@ -3554,7 +3542,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>42748</v>
       </c>
       <c r="B108" t="n">
@@ -3583,7 +3571,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>42755</v>
       </c>
       <c r="B109" t="n">
@@ -3612,7 +3600,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>42762</v>
       </c>
       <c r="B110" t="n">
@@ -3641,7 +3629,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="B111" t="n">
@@ -3670,7 +3658,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>42776</v>
       </c>
       <c r="B112" t="n">
@@ -3699,7 +3687,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>42783</v>
       </c>
       <c r="B113" t="n">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>42790</v>
       </c>
       <c r="B114" t="n">
@@ -3757,7 +3745,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>42797</v>
       </c>
       <c r="B115" t="n">
@@ -3786,7 +3774,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>42804</v>
       </c>
       <c r="B116" t="n">
@@ -3815,7 +3803,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="B117" t="n">
@@ -3844,7 +3832,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>42818</v>
       </c>
       <c r="B118" t="n">
@@ -3873,7 +3861,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B119" t="n">
@@ -3902,7 +3890,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>42832</v>
       </c>
       <c r="B120" t="n">
@@ -3931,7 +3919,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>42839</v>
       </c>
       <c r="B121" t="n">
@@ -3960,7 +3948,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42846</v>
       </c>
       <c r="B122" t="n">
@@ -3989,7 +3977,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42853</v>
       </c>
       <c r="B123" t="n">
@@ -4018,7 +4006,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42860</v>
       </c>
       <c r="B124" t="n">
@@ -4047,7 +4035,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42867</v>
       </c>
       <c r="B125" t="n">
@@ -4076,7 +4064,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42874</v>
       </c>
       <c r="B126" t="n">
@@ -4105,7 +4093,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42881</v>
       </c>
       <c r="B127" t="n">
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42888</v>
       </c>
       <c r="B128" t="n">
@@ -4163,7 +4151,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42895</v>
       </c>
       <c r="B129" t="n">
@@ -4192,7 +4180,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42902</v>
       </c>
       <c r="B130" t="n">
@@ -4221,7 +4209,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42909</v>
       </c>
       <c r="B131" t="n">
@@ -4250,7 +4238,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B132" t="n">
@@ -4279,7 +4267,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42923</v>
       </c>
       <c r="B133" t="n">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42930</v>
       </c>
       <c r="B134" t="n">
@@ -4337,7 +4325,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42937</v>
       </c>
       <c r="B135" t="n">
@@ -4366,7 +4354,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42944</v>
       </c>
       <c r="B136" t="n">
@@ -4395,7 +4383,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42951</v>
       </c>
       <c r="B137" t="n">
@@ -4424,7 +4412,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42958</v>
       </c>
       <c r="B138" t="n">
@@ -4453,7 +4441,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42965</v>
       </c>
       <c r="B139" t="n">
@@ -4482,7 +4470,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42972</v>
       </c>
       <c r="B140" t="n">
@@ -4511,7 +4499,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B141" t="n">
@@ -4540,7 +4528,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42986</v>
       </c>
       <c r="B142" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42993</v>
       </c>
       <c r="B143" t="n">
@@ -4598,7 +4586,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>43000</v>
       </c>
       <c r="B144" t="n">
@@ -4627,7 +4615,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>43007</v>
       </c>
       <c r="B145" t="n">
@@ -4656,7 +4644,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>43014</v>
       </c>
       <c r="B146" t="n">
@@ -4685,7 +4673,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>43021</v>
       </c>
       <c r="B147" t="n">
@@ -4714,7 +4702,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>43028</v>
       </c>
       <c r="B148" t="n">
@@ -4743,7 +4731,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>43035</v>
       </c>
       <c r="B149" t="n">
@@ -4772,7 +4760,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>43042</v>
       </c>
       <c r="B150" t="n">
@@ -4801,7 +4789,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>43049</v>
       </c>
       <c r="B151" t="n">
@@ -4830,7 +4818,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43056</v>
       </c>
       <c r="B152" t="n">
@@ -4859,7 +4847,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43063</v>
       </c>
       <c r="B153" t="n">
@@ -4888,7 +4876,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B154" t="n">
@@ -4917,7 +4905,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="B155" t="n">
@@ -4946,7 +4934,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43084</v>
       </c>
       <c r="B156" t="n">
@@ -4975,7 +4963,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43091</v>
       </c>
       <c r="B157" t="n">
@@ -5004,7 +4992,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="B158" t="n">
@@ -5033,7 +5021,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43105</v>
       </c>
       <c r="B159" t="n">
@@ -5062,7 +5050,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="B160" t="n">
@@ -5091,7 +5079,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43119</v>
       </c>
       <c r="B161" t="n">
@@ -5120,7 +5108,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43126</v>
       </c>
       <c r="B162" t="n">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43133</v>
       </c>
       <c r="B163" t="n">
@@ -5178,7 +5166,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43140</v>
       </c>
       <c r="B164" t="n">
@@ -5207,7 +5195,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43147</v>
       </c>
       <c r="B165" t="n">
@@ -5236,7 +5224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43154</v>
       </c>
       <c r="B166" t="n">
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43161</v>
       </c>
       <c r="B167" t="n">
@@ -5294,7 +5282,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43168</v>
       </c>
       <c r="B168" t="n">
@@ -5323,7 +5311,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43175</v>
       </c>
       <c r="B169" t="n">
@@ -5352,7 +5340,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43182</v>
       </c>
       <c r="B170" t="n">
@@ -5381,7 +5369,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="B171" t="n">
@@ -5410,7 +5398,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43196</v>
       </c>
       <c r="B172" t="n">
@@ -5439,7 +5427,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43203</v>
       </c>
       <c r="B173" t="n">
@@ -5468,7 +5456,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43210</v>
       </c>
       <c r="B174" t="n">
@@ -5497,7 +5485,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43217</v>
       </c>
       <c r="B175" t="n">
@@ -5526,7 +5514,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="B176" t="n">
@@ -5555,7 +5543,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43231</v>
       </c>
       <c r="B177" t="n">
@@ -5584,7 +5572,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43238</v>
       </c>
       <c r="B178" t="n">
@@ -5613,7 +5601,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43245</v>
       </c>
       <c r="B179" t="n">
@@ -5642,7 +5630,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B180" t="n">
@@ -5671,7 +5659,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43259</v>
       </c>
       <c r="B181" t="n">
@@ -5700,7 +5688,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43266</v>
       </c>
       <c r="B182" t="n">
@@ -5729,7 +5717,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43273</v>
       </c>
       <c r="B183" t="n">
@@ -5758,7 +5746,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43280</v>
       </c>
       <c r="B184" t="n">
@@ -5787,7 +5775,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43287</v>
       </c>
       <c r="B185" t="n">
@@ -5816,7 +5804,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43294</v>
       </c>
       <c r="B186" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43301</v>
       </c>
       <c r="B187" t="n">
@@ -5874,7 +5862,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43308</v>
       </c>
       <c r="B188" t="n">
@@ -5903,7 +5891,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="B189" t="n">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43322</v>
       </c>
       <c r="B190" t="n">
@@ -5961,7 +5949,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43329</v>
       </c>
       <c r="B191" t="n">
@@ -5990,7 +5978,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43336</v>
       </c>
       <c r="B192" t="n">
@@ -6019,7 +6007,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B193" t="n">
@@ -6048,7 +6036,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43350</v>
       </c>
       <c r="B194" t="n">
@@ -6077,7 +6065,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43357</v>
       </c>
       <c r="B195" t="n">
@@ -6106,7 +6094,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43364</v>
       </c>
       <c r="B196" t="n">
@@ -6135,7 +6123,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43371</v>
       </c>
       <c r="B197" t="n">
@@ -6164,7 +6152,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43378</v>
       </c>
       <c r="B198" t="n">
@@ -6193,7 +6181,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43385</v>
       </c>
       <c r="B199" t="n">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>43392</v>
       </c>
       <c r="B200" t="n">
@@ -6251,7 +6239,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>43399</v>
       </c>
       <c r="B201" t="n">
@@ -6280,7 +6268,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>43406</v>
       </c>
       <c r="B202" t="n">
@@ -6309,7 +6297,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>43413</v>
       </c>
       <c r="B203" t="n">
@@ -6338,7 +6326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>43420</v>
       </c>
       <c r="B204" t="n">
@@ -6367,7 +6355,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>43427</v>
       </c>
       <c r="B205" t="n">
@@ -6396,7 +6384,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B206" t="n">
@@ -6425,7 +6413,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>43441</v>
       </c>
       <c r="B207" t="n">
@@ -6454,7 +6442,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>43448</v>
       </c>
       <c r="B208" t="n">
@@ -6483,7 +6471,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>43455</v>
       </c>
       <c r="B209" t="n">
@@ -6512,7 +6500,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>43462</v>
       </c>
       <c r="B210" t="n">
@@ -6541,7 +6529,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>43469</v>
       </c>
       <c r="B211" t="n">
@@ -6570,7 +6558,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>43476</v>
       </c>
       <c r="B212" t="n">
@@ -6599,7 +6587,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="B213" t="n">
@@ -6628,7 +6616,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>43490</v>
       </c>
       <c r="B214" t="n">
@@ -6657,7 +6645,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B215" t="n">
@@ -6686,7 +6674,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>43504</v>
       </c>
       <c r="B216" t="n">
@@ -6715,7 +6703,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>43511</v>
       </c>
       <c r="B217" t="n">
@@ -6744,7 +6732,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>43518</v>
       </c>
       <c r="B218" t="n">
@@ -6773,7 +6761,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B219" t="n">
@@ -6802,7 +6790,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="B220" t="n">
@@ -6831,7 +6819,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>43539</v>
       </c>
       <c r="B221" t="n">
@@ -6860,7 +6848,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>43546</v>
       </c>
       <c r="B222" t="n">
@@ -6889,7 +6877,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>43553</v>
       </c>
       <c r="B223" t="n">
@@ -6918,7 +6906,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>43560</v>
       </c>
       <c r="B224" t="n">
@@ -6947,7 +6935,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>43567</v>
       </c>
       <c r="B225" t="n">
@@ -6976,7 +6964,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>43574</v>
       </c>
       <c r="B226" t="n">
@@ -7005,7 +6993,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>43581</v>
       </c>
       <c r="B227" t="n">
@@ -7034,7 +7022,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43588</v>
       </c>
       <c r="B228" t="n">
@@ -7063,7 +7051,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43595</v>
       </c>
       <c r="B229" t="n">
@@ -7092,7 +7080,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43602</v>
       </c>
       <c r="B230" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43609</v>
       </c>
       <c r="B231" t="n">
@@ -7150,7 +7138,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B232" t="n">
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43623</v>
       </c>
       <c r="B233" t="n">
@@ -7208,7 +7196,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43630</v>
       </c>
       <c r="B234" t="n">
@@ -7237,7 +7225,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43637</v>
       </c>
       <c r="B235" t="n">
@@ -7266,7 +7254,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43644</v>
       </c>
       <c r="B236" t="n">
@@ -7295,7 +7283,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43651</v>
       </c>
       <c r="B237" t="n">
@@ -7324,7 +7312,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43658</v>
       </c>
       <c r="B238" t="n">
@@ -7353,7 +7341,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>43665</v>
       </c>
       <c r="B239" t="n">
@@ -7382,7 +7370,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>43672</v>
       </c>
       <c r="B240" t="n">
@@ -7411,7 +7399,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="B241" t="n">
@@ -7440,7 +7428,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>43686</v>
       </c>
       <c r="B242" t="n">
@@ -7469,7 +7457,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>43693</v>
       </c>
       <c r="B243" t="n">
@@ -7498,7 +7486,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>43700</v>
       </c>
       <c r="B244" t="n">
@@ -7527,7 +7515,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>43707</v>
       </c>
       <c r="B245" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>43714</v>
       </c>
       <c r="B246" t="n">
@@ -7585,7 +7573,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>43721</v>
       </c>
       <c r="B247" t="n">
@@ -7614,7 +7602,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>43728</v>
       </c>
       <c r="B248" t="n">
@@ -7643,7 +7631,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>43735</v>
       </c>
       <c r="B249" t="n">
@@ -7672,7 +7660,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>43742</v>
       </c>
       <c r="B250" t="n">
@@ -7701,7 +7689,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>43749</v>
       </c>
       <c r="B251" t="n">
@@ -7730,7 +7718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>43756</v>
       </c>
       <c r="B252" t="n">
@@ -7759,7 +7747,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>43763</v>
       </c>
       <c r="B253" t="n">
@@ -7788,7 +7776,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B254" t="n">
@@ -7817,7 +7805,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>43777</v>
       </c>
       <c r="B255" t="n">
@@ -7846,7 +7834,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>43784</v>
       </c>
       <c r="B256" t="n">
@@ -7875,7 +7863,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>43791</v>
       </c>
       <c r="B257" t="n">
@@ -7904,7 +7892,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="B258" t="n">
@@ -7933,7 +7921,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>43805</v>
       </c>
       <c r="B259" t="n">
@@ -7962,7 +7950,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="B260" t="n">
@@ -7991,7 +7979,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>43819</v>
       </c>
       <c r="B261" t="n">
@@ -8020,7 +8008,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="B262" t="n">
@@ -8049,7 +8037,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>43833</v>
       </c>
       <c r="B263" t="n">
@@ -8078,7 +8066,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>43840</v>
       </c>
       <c r="B264" t="n">
@@ -8107,7 +8095,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43847</v>
       </c>
       <c r="B265" t="n">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43854</v>
       </c>
       <c r="B266" t="n">
@@ -8165,7 +8153,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B267" t="n">
@@ -8194,7 +8182,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43868</v>
       </c>
       <c r="B268" t="n">
@@ -8223,7 +8211,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43875</v>
       </c>
       <c r="B269" t="n">
@@ -8252,7 +8240,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="B270" t="n">
@@ -8281,7 +8269,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43889</v>
       </c>
       <c r="B271" t="n">
@@ -8310,7 +8298,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43896</v>
       </c>
       <c r="B272" t="n">
@@ -8339,7 +8327,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43903</v>
       </c>
       <c r="B273" t="n">
@@ -8368,7 +8356,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43910</v>
       </c>
       <c r="B274" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43917</v>
       </c>
       <c r="B275" t="n">
@@ -8426,7 +8414,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43924</v>
       </c>
       <c r="B276" t="n">
@@ -8455,7 +8443,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43931</v>
       </c>
       <c r="B277" t="n">
@@ -8484,7 +8472,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43938</v>
       </c>
       <c r="B278" t="n">
@@ -8513,7 +8501,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43945</v>
       </c>
       <c r="B279" t="n">
@@ -8542,7 +8530,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B280" t="n">
@@ -8571,7 +8559,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43959</v>
       </c>
       <c r="B281" t="n">
@@ -8600,7 +8588,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43966</v>
       </c>
       <c r="B282" t="n">
@@ -8629,7 +8617,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>43973</v>
       </c>
       <c r="B283" t="n">
@@ -8658,7 +8646,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>43980</v>
       </c>
       <c r="B284" t="n">
@@ -8687,7 +8675,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>43987</v>
       </c>
       <c r="B285" t="n">
@@ -8716,7 +8704,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>43994</v>
       </c>
       <c r="B286" t="n">
@@ -8745,7 +8733,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44001</v>
       </c>
       <c r="B287" t="n">
@@ -8774,7 +8762,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44008</v>
       </c>
       <c r="B288" t="n">
@@ -8803,7 +8791,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44015</v>
       </c>
       <c r="B289" t="n">
@@ -8832,7 +8820,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44022</v>
       </c>
       <c r="B290" t="n">
@@ -8861,7 +8849,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44029</v>
       </c>
       <c r="B291" t="n">
@@ -8890,7 +8878,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44036</v>
       </c>
       <c r="B292" t="n">
@@ -8919,7 +8907,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B293" t="n">
@@ -8948,7 +8936,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44050</v>
       </c>
       <c r="B294" t="n">
@@ -8977,7 +8965,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44057</v>
       </c>
       <c r="B295" t="n">
@@ -9006,7 +8994,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44064</v>
       </c>
       <c r="B296" t="n">
@@ -9035,7 +9023,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44071</v>
       </c>
       <c r="B297" t="n">
@@ -9064,7 +9052,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44078</v>
       </c>
       <c r="B298" t="n">
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44085</v>
       </c>
       <c r="B299" t="n">
@@ -9122,7 +9110,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="B300" t="n">
@@ -9151,7 +9139,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44099</v>
       </c>
       <c r="B301" t="n">
@@ -9180,7 +9168,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44106</v>
       </c>
       <c r="B302" t="n">
@@ -9209,7 +9197,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44113</v>
       </c>
       <c r="B303" t="n">
@@ -9238,7 +9226,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44120</v>
       </c>
       <c r="B304" t="n">
@@ -9267,7 +9255,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>44127</v>
       </c>
       <c r="B305" t="n">
@@ -9296,7 +9284,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>44134</v>
       </c>
       <c r="B306" t="n">
@@ -9325,7 +9313,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>44141</v>
       </c>
       <c r="B307" t="n">
@@ -9354,7 +9342,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>44148</v>
       </c>
       <c r="B308" t="n">
@@ -9383,7 +9371,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>44155</v>
       </c>
       <c r="B309" t="n">
@@ -9412,7 +9400,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>44162</v>
       </c>
       <c r="B310" t="n">
@@ -9441,7 +9429,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>44169</v>
       </c>
       <c r="B311" t="n">
@@ -9470,7 +9458,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>44176</v>
       </c>
       <c r="B312" t="n">
@@ -9499,7 +9487,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>44183</v>
       </c>
       <c r="B313" t="n">
@@ -9528,7 +9516,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>44190</v>
       </c>
       <c r="B314" t="n">
@@ -9557,7 +9545,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B315" t="n">
@@ -9586,7 +9574,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>44204</v>
       </c>
       <c r="B316" t="n">
@@ -9615,7 +9603,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>44211</v>
       </c>
       <c r="B317" t="n">
@@ -9644,7 +9632,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>44218</v>
       </c>
       <c r="B318" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>44225</v>
       </c>
       <c r="B319" t="n">
@@ -9702,7 +9690,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>44232</v>
       </c>
       <c r="B320" t="n">
@@ -9731,7 +9719,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>44239</v>
       </c>
       <c r="B321" t="n">
@@ -9760,7 +9748,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>44246</v>
       </c>
       <c r="B322" t="n">
@@ -9789,7 +9777,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>44253</v>
       </c>
       <c r="B323" t="n">
@@ -9818,7 +9806,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>44260</v>
       </c>
       <c r="B324" t="n">
@@ -9847,7 +9835,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="B325" t="n">
@@ -9876,7 +9864,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44274</v>
       </c>
       <c r="B326" t="n">
@@ -9905,7 +9893,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="B327" t="n">
@@ -9934,7 +9922,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44288</v>
       </c>
       <c r="B328" t="n">
@@ -9963,7 +9951,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44295</v>
       </c>
       <c r="B329" t="n">
@@ -9992,7 +9980,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="B330" t="n">
@@ -10021,7 +10009,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44309</v>
       </c>
       <c r="B331" t="n">
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B332" t="n">
@@ -10079,7 +10067,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="B333" t="n">
@@ -10108,7 +10096,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44330</v>
       </c>
       <c r="B334" t="n">
@@ -10137,7 +10125,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44337</v>
       </c>
       <c r="B335" t="n">
@@ -10166,7 +10154,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="B336" t="n">
@@ -10195,7 +10183,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44351</v>
       </c>
       <c r="B337" t="n">
@@ -10224,7 +10212,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44358</v>
       </c>
       <c r="B338" t="n">
@@ -10253,7 +10241,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="B339" t="n">
@@ -10282,7 +10270,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44372</v>
       </c>
       <c r="B340" t="n">
@@ -10311,7 +10299,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44379</v>
       </c>
       <c r="B341" t="n">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44386</v>
       </c>
       <c r="B342" t="n">
@@ -10369,7 +10357,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44393</v>
       </c>
       <c r="B343" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44400</v>
       </c>
       <c r="B344" t="n">
@@ -10427,7 +10415,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44407</v>
       </c>
       <c r="B345" t="n">
@@ -10456,7 +10444,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44414</v>
       </c>
       <c r="B346" t="n">
@@ -10485,7 +10473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="B347" t="n">
@@ -10514,7 +10502,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44428</v>
       </c>
       <c r="B348" t="n">
@@ -10543,7 +10531,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44435</v>
       </c>
       <c r="B349" t="n">
@@ -10572,7 +10560,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>44442</v>
       </c>
       <c r="B350" t="n">
@@ -10601,7 +10589,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>44449</v>
       </c>
       <c r="B351" t="n">
@@ -10630,7 +10618,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>44456</v>
       </c>
       <c r="B352" t="n">
@@ -10659,7 +10647,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>44463</v>
       </c>
       <c r="B353" t="n">
@@ -10688,7 +10676,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B354" t="n">
@@ -10717,7 +10705,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>44477</v>
       </c>
       <c r="B355" t="n">
@@ -10746,7 +10734,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>44484</v>
       </c>
       <c r="B356" t="n">
@@ -10775,7 +10763,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>44491</v>
       </c>
       <c r="B357" t="n">
@@ -10804,7 +10792,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="B358" t="n">
@@ -10833,7 +10821,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>44505</v>
       </c>
       <c r="B359" t="n">
@@ -10862,7 +10850,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>44512</v>
       </c>
       <c r="B360" t="n">
@@ -10891,7 +10879,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>44519</v>
       </c>
       <c r="B361" t="n">
@@ -10920,7 +10908,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>44526</v>
       </c>
       <c r="B362" t="n">
@@ -10949,7 +10937,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>44533</v>
       </c>
       <c r="B363" t="n">
@@ -10978,7 +10966,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>44540</v>
       </c>
       <c r="B364" t="n">
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>44547</v>
       </c>
       <c r="B365" t="n">
@@ -11036,7 +11024,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>44554</v>
       </c>
       <c r="B366" t="n">
@@ -11065,7 +11053,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B367" t="n">
@@ -11094,7 +11082,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>44568</v>
       </c>
       <c r="B368" t="n">
@@ -11123,7 +11111,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>44575</v>
       </c>
       <c r="B369" t="n">
@@ -11152,7 +11140,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>44582</v>
       </c>
       <c r="B370" t="n">
@@ -11181,7 +11169,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>44589</v>
       </c>
       <c r="B371" t="n">
@@ -11210,7 +11198,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>44596</v>
       </c>
       <c r="B372" t="n">
@@ -11239,7 +11227,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>44603</v>
       </c>
       <c r="B373" t="n">
@@ -11268,7 +11256,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>44610</v>
       </c>
       <c r="B374" t="n">
@@ -11297,7 +11285,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>44617</v>
       </c>
       <c r="B375" t="n">
@@ -11326,7 +11314,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>44624</v>
       </c>
       <c r="B376" t="n">
@@ -11355,7 +11343,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>44631</v>
       </c>
       <c r="B377" t="n">
@@ -11384,7 +11372,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>44638</v>
       </c>
       <c r="B378" t="n">
@@ -11413,7 +11401,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>44645</v>
       </c>
       <c r="B379" t="n">
@@ -11442,7 +11430,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B380" t="n">
@@ -11471,7 +11459,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>44659</v>
       </c>
       <c r="B381" t="n">
@@ -11500,7 +11488,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>44666</v>
       </c>
       <c r="B382" t="n">
@@ -11529,7 +11517,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>44673</v>
       </c>
       <c r="B383" t="n">
@@ -11558,7 +11546,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>44680</v>
       </c>
       <c r="B384" t="n">
@@ -11587,7 +11575,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>44687</v>
       </c>
       <c r="B385" t="n">
@@ -11616,7 +11604,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>44694</v>
       </c>
       <c r="B386" t="n">
@@ -11645,7 +11633,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>44701</v>
       </c>
       <c r="B387" t="n">
@@ -11674,7 +11662,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>44708</v>
       </c>
       <c r="B388" t="n">
@@ -11703,7 +11691,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>44715</v>
       </c>
       <c r="B389" t="n">
@@ -11732,7 +11720,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>44722</v>
       </c>
       <c r="B390" t="n">
@@ -11761,7 +11749,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>44729</v>
       </c>
       <c r="B391" t="n">
@@ -11790,7 +11778,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>44736</v>
       </c>
       <c r="B392" t="n">
@@ -11819,7 +11807,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B393" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>44750</v>
       </c>
       <c r="B394" t="n">
@@ -11877,7 +11865,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>44757</v>
       </c>
       <c r="B395" t="n">
@@ -11906,7 +11894,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>44764</v>
       </c>
       <c r="B396" t="n">
@@ -11935,7 +11923,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>44771</v>
       </c>
       <c r="B397" t="n">
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="B398" t="n">
@@ -11993,7 +11981,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>44785</v>
       </c>
       <c r="B399" t="n">
@@ -12022,7 +12010,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>44792</v>
       </c>
       <c r="B400" t="n">
@@ -12051,7 +12039,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>44799</v>
       </c>
       <c r="B401" t="n">
@@ -12080,7 +12068,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>44806</v>
       </c>
       <c r="B402" t="n">
@@ -12109,7 +12097,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>44813</v>
       </c>
       <c r="B403" t="n">
@@ -12138,7 +12126,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>44820</v>
       </c>
       <c r="B404" t="n">
@@ -12167,7 +12155,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>44827</v>
       </c>
       <c r="B405" t="n">
@@ -12196,7 +12184,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B406" t="n">
@@ -12225,7 +12213,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>44841</v>
       </c>
       <c r="B407" t="n">
@@ -12254,7 +12242,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>44848</v>
       </c>
       <c r="B408" t="n">
@@ -12283,7 +12271,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>44855</v>
       </c>
       <c r="B409" t="n">
@@ -12312,7 +12300,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>44862</v>
       </c>
       <c r="B410" t="n">
@@ -12341,7 +12329,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>44869</v>
       </c>
       <c r="B411" t="n">
@@ -12370,7 +12358,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>44876</v>
       </c>
       <c r="B412" t="n">
@@ -12399,7 +12387,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>44883</v>
       </c>
       <c r="B413" t="n">
@@ -12428,7 +12416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>44890</v>
       </c>
       <c r="B414" t="n">
@@ -12457,7 +12445,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>44897</v>
       </c>
       <c r="B415" t="n">
@@ -12486,7 +12474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>44904</v>
       </c>
       <c r="B416" t="n">
@@ -12515,7 +12503,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>44911</v>
       </c>
       <c r="B417" t="n">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>44918</v>
       </c>
       <c r="B418" t="n">
@@ -12573,7 +12561,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>44925</v>
       </c>
       <c r="B419" t="n">
@@ -12602,7 +12590,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>44932</v>
       </c>
       <c r="B420" t="n">
@@ -12631,7 +12619,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>44939</v>
       </c>
       <c r="B421" t="n">
@@ -12660,7 +12648,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>44946</v>
       </c>
       <c r="B422" t="n">
@@ -12689,7 +12677,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>44953</v>
       </c>
       <c r="B423" t="n">
@@ -12718,7 +12706,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>44960</v>
       </c>
       <c r="B424" t="n">
@@ -12747,7 +12735,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>44967</v>
       </c>
       <c r="B425" t="n">
@@ -12776,7 +12764,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>44974</v>
       </c>
       <c r="B426" t="n">
@@ -12805,7 +12793,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44981</v>
       </c>
       <c r="B427" t="n">
@@ -12834,7 +12822,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44988</v>
       </c>
       <c r="B428" t="n">
@@ -12863,7 +12851,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44995</v>
       </c>
       <c r="B429" t="n">
@@ -12892,7 +12880,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>45002</v>
       </c>
       <c r="B430" t="n">
@@ -12921,7 +12909,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>45009</v>
       </c>
       <c r="B431" t="n">
@@ -12950,7 +12938,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B432" t="n">
@@ -12979,7 +12967,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>45023</v>
       </c>
       <c r="B433" t="n">
@@ -13008,7 +12996,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>45030</v>
       </c>
       <c r="B434" t="n">
@@ -13037,7 +13025,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="B435" t="n">
@@ -13066,7 +13054,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>45044</v>
       </c>
       <c r="B436" t="n">
@@ -13095,7 +13083,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>45051</v>
       </c>
       <c r="B437" t="n">
@@ -13124,7 +13112,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>45058</v>
       </c>
       <c r="B438" t="n">
@@ -13153,7 +13141,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>45065</v>
       </c>
       <c r="B439" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>45072</v>
       </c>
       <c r="B440" t="n">
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>45079</v>
       </c>
       <c r="B441" t="n">
@@ -13240,7 +13228,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>45086</v>
       </c>
       <c r="B442" t="n">
@@ -13269,7 +13257,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>45093</v>
       </c>
       <c r="B443" t="n">
@@ -13298,7 +13286,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>45100</v>
       </c>
       <c r="B444" t="n">
@@ -13327,7 +13315,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B445" t="n">
@@ -13356,7 +13344,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="B446" t="n">
@@ -13385,7 +13373,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>45121</v>
       </c>
       <c r="B447" t="n">
@@ -13414,7 +13402,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>45128</v>
       </c>
       <c r="B448" t="n">
@@ -13443,7 +13431,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>45135</v>
       </c>
       <c r="B449" t="n">
@@ -13472,7 +13460,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>45142</v>
       </c>
       <c r="B450" t="n">
@@ -13501,7 +13489,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="B451" t="n">
@@ -13530,7 +13518,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>45156</v>
       </c>
       <c r="B452" t="n">
@@ -13559,7 +13547,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>45163</v>
       </c>
       <c r="B453" t="n">
@@ -13588,7 +13576,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B454" t="n">
@@ -13617,7 +13605,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>45177</v>
       </c>
       <c r="B455" t="n">
@@ -13646,7 +13634,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>45184</v>
       </c>
       <c r="B456" t="n">
@@ -13675,7 +13663,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>45191</v>
       </c>
       <c r="B457" t="n">
@@ -13704,7 +13692,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>45198</v>
       </c>
       <c r="B458" t="n">
@@ -13733,7 +13721,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>45205</v>
       </c>
       <c r="B459" t="n">
@@ -13762,7 +13750,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45212</v>
       </c>
       <c r="B460" t="n">
@@ -13791,7 +13779,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45219</v>
       </c>
       <c r="B461" t="n">
@@ -13820,7 +13808,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45226</v>
       </c>
       <c r="B462" t="n">
@@ -13849,7 +13837,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45233</v>
       </c>
       <c r="B463" t="n">
@@ -13878,7 +13866,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45240</v>
       </c>
       <c r="B464" t="n">
@@ -13907,7 +13895,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="B465" t="n">
@@ -13936,7 +13924,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="B466" t="n">
@@ -13965,7 +13953,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B467" t="n">
@@ -13994,7 +13982,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45268</v>
       </c>
       <c r="B468" t="n">
@@ -14023,7 +14011,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="B469" t="n">
@@ -14052,7 +14040,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="B470" t="n">
@@ -14081,7 +14069,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45289</v>
       </c>
       <c r="B471" t="n">
@@ -14110,7 +14098,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="B472" t="n">
@@ -14139,7 +14127,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45303</v>
       </c>
       <c r="B473" t="n">
@@ -14168,7 +14156,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45310</v>
       </c>
       <c r="B474" t="n">
@@ -14197,7 +14185,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="B475" t="n">
@@ -14226,7 +14214,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45324</v>
       </c>
       <c r="B476" t="n">
@@ -14255,7 +14243,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45331</v>
       </c>
       <c r="B477" t="n">
@@ -14284,7 +14272,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45338</v>
       </c>
       <c r="B478" t="n">
@@ -14313,7 +14301,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45345</v>
       </c>
       <c r="B479" t="n">
@@ -14342,7 +14330,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B480" t="n">
@@ -14371,7 +14359,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45359</v>
       </c>
       <c r="B481" t="n">
@@ -14400,7 +14388,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="B482" t="n">
@@ -14429,7 +14417,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="B483" t="n">
@@ -14458,7 +14446,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="B484" t="n">
@@ -14487,7 +14475,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="B485" t="n">
@@ -14516,7 +14504,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="B486" t="n">
@@ -14545,7 +14533,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45401</v>
       </c>
       <c r="B487" t="n">
@@ -14574,7 +14562,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45408</v>
       </c>
       <c r="B488" t="n">
@@ -14603,7 +14591,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45415</v>
       </c>
       <c r="B489" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45422</v>
       </c>
       <c r="B490" t="n">
@@ -14661,7 +14649,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45429</v>
       </c>
       <c r="B491" t="n">
@@ -14690,7 +14678,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45436</v>
       </c>
       <c r="B492" t="n">
@@ -14719,7 +14707,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B493" t="n">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="B494" t="n">
@@ -14777,7 +14765,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="B495" t="n">
@@ -14806,7 +14794,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="B496" t="n">
@@ -14835,7 +14823,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="B497" t="n">
@@ -14864,7 +14852,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>45478</v>
       </c>
       <c r="B498" t="n">
@@ -14893,7 +14881,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="B499" t="n">
@@ -14922,7 +14910,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>45492</v>
       </c>
       <c r="B500" t="n">
@@ -14951,7 +14939,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="B501" t="n">
@@ -14980,7 +14968,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>45506</v>
       </c>
       <c r="B502" t="n">
@@ -15009,7 +14997,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="2" t="n">
+      <c r="A503" s="1" t="n">
         <v>45513</v>
       </c>
       <c r="B503" t="n">
@@ -15038,7 +15026,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="2" t="n">
+      <c r="A504" s="1" t="n">
         <v>45520</v>
       </c>
       <c r="B504" t="n">
@@ -15067,7 +15055,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="2" t="n">
+      <c r="A505" s="1" t="n">
         <v>45527</v>
       </c>
       <c r="B505" t="n">
@@ -15096,7 +15084,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="2" t="n">
+      <c r="A506" s="1" t="n">
         <v>45534</v>
       </c>
       <c r="B506" t="n">
@@ -15125,7 +15113,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="2" t="n">
+      <c r="A507" s="1" t="n">
         <v>45541</v>
       </c>
       <c r="B507" t="n">
@@ -15154,7 +15142,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="2" t="n">
+      <c r="A508" s="1" t="n">
         <v>45548</v>
       </c>
       <c r="B508" t="n">
@@ -15183,7 +15171,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="2" t="n">
+      <c r="A509" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="B509" t="n">
@@ -15212,7 +15200,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="2" t="n">
+      <c r="A510" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="B510" t="n">
@@ -15241,7 +15229,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="2" t="n">
+      <c r="A511" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="B511" t="n">
@@ -15270,7 +15258,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="2" t="n">
+      <c r="A512" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="B512" t="n">
@@ -15299,7 +15287,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="2" t="n">
+      <c r="A513" s="1" t="n">
         <v>45583</v>
       </c>
       <c r="B513" t="n">
@@ -15328,7 +15316,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="2" t="n">
+      <c r="A514" s="1" t="n">
         <v>45590</v>
       </c>
       <c r="B514" t="n">
@@ -15357,7 +15345,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="2" t="n">
+      <c r="A515" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B515" t="n">
@@ -15386,7 +15374,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="2" t="n">
+      <c r="A516" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="B516" t="n">
@@ -15415,7 +15403,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="2" t="n">
+      <c r="A517" s="1" t="n">
         <v>45611</v>
       </c>
       <c r="B517" t="n">
@@ -15444,7 +15432,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="2" t="n">
+      <c r="A518" s="1" t="n">
         <v>45618</v>
       </c>
       <c r="B518" t="n">
@@ -15473,7 +15461,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="2" t="n">
+      <c r="A519" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="B519" t="n">
@@ -15502,7 +15490,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="2" t="n">
+      <c r="A520" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="B520" t="n">
@@ -15531,7 +15519,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="2" t="n">
+      <c r="A521" s="1" t="n">
         <v>45639</v>
       </c>
       <c r="B521" t="n">
@@ -15560,7 +15548,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="2" t="n">
+      <c r="A522" s="1" t="n">
         <v>45646</v>
       </c>
       <c r="B522" t="n">
@@ -15589,7 +15577,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="2" t="n">
+      <c r="A523" s="1" t="n">
         <v>45653</v>
       </c>
       <c r="B523" t="n">
@@ -15618,7 +15606,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="2" t="n">
+      <c r="A524" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="B524" t="n">
@@ -15647,7 +15635,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="2" t="n">
+      <c r="A525" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="B525" t="n">
@@ -15676,7 +15664,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="2" t="n">
+      <c r="A526" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="B526" t="n">
@@ -15705,7 +15693,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="2" t="n">
+      <c r="A527" s="1" t="n">
         <v>45681</v>
       </c>
       <c r="B527" t="n">
@@ -15734,7 +15722,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="2" t="n">
+      <c r="A528" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B528" t="n">
@@ -15763,7 +15751,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="2" t="n">
+      <c r="A529" s="1" t="n">
         <v>45695</v>
       </c>
       <c r="B529" t="n">
@@ -15792,7 +15780,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="2" t="n">
+      <c r="A530" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="B530" t="n">
@@ -15821,7 +15809,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="2" t="n">
+      <c r="A531" s="1" t="n">
         <v>45709</v>
       </c>
       <c r="B531" t="n">
@@ -15850,7 +15838,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="2" t="n">
+      <c r="A532" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B532" t="n">
@@ -15879,7 +15867,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="2" t="n">
+      <c r="A533" s="1" t="n">
         <v>45723</v>
       </c>
       <c r="B533" t="n">
@@ -15908,7 +15896,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="2" t="n">
+      <c r="A534" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="B534" t="n">
@@ -15937,7 +15925,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="2" t="n">
+      <c r="A535" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="B535" t="n">
@@ -15966,7 +15954,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="2" t="n">
+      <c r="A536" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="B536" t="n">
@@ -15995,7 +15983,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="2" t="n">
+      <c r="A537" s="1" t="n">
         <v>45751</v>
       </c>
       <c r="B537" t="n">
@@ -16024,7 +16012,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="2" t="n">
+      <c r="A538" s="1" t="n">
         <v>45758</v>
       </c>
       <c r="B538" t="n">
@@ -16053,7 +16041,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="2" t="n">
+      <c r="A539" s="1" t="n">
         <v>45765</v>
       </c>
       <c r="B539" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="2" t="n">
+      <c r="A540" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="B540" t="n">
@@ -16111,7 +16099,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="2" t="n">
+      <c r="A541" s="1" t="n">
         <v>45779</v>
       </c>
       <c r="B541" t="n">
@@ -16140,7 +16128,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="2" t="n">
+      <c r="A542" s="1" t="n">
         <v>45786</v>
       </c>
       <c r="B542" t="n">
@@ -16169,7 +16157,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="2" t="n">
+      <c r="A543" s="1" t="n">
         <v>45793</v>
       </c>
       <c r="B543" t="n">
@@ -16198,7 +16186,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="2" t="n">
+      <c r="A544" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="B544" t="n">
@@ -16227,7 +16215,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="2" t="n">
+      <c r="A545" s="1" t="n">
         <v>45807</v>
       </c>
       <c r="B545" t="n">
@@ -16256,7 +16244,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="2" t="n">
+      <c r="A546" s="1" t="n">
         <v>45814</v>
       </c>
       <c r="B546" t="n">
@@ -16285,7 +16273,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="2" t="n">
+      <c r="A547" s="1" t="n">
         <v>45821</v>
       </c>
       <c r="B547" t="n">
@@ -16314,7 +16302,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="2" t="n">
+      <c r="A548" s="1" t="n">
         <v>45828</v>
       </c>
       <c r="B548" t="n">
@@ -16343,7 +16331,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="2" t="n">
+      <c r="A549" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="B549" t="n">
@@ -16372,7 +16360,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="2" t="n">
+      <c r="A550" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="B550" t="n">
@@ -16401,7 +16389,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="2" t="n">
+      <c r="A551" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="B551" t="n">
@@ -16430,7 +16418,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="2" t="n">
+      <c r="A552" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="B552" t="n">
@@ -16459,7 +16447,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="2" t="n">
+      <c r="A553" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="B553" t="n">
@@ -16488,7 +16476,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="2" t="n">
+      <c r="A554" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B554" t="n">
@@ -16517,7 +16505,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="2" t="n">
+      <c r="A555" s="1" t="n">
         <v>45877</v>
       </c>
       <c r="B555" t="n">
@@ -16546,7 +16534,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="2" t="n">
+      <c r="A556" s="1" t="n">
         <v>45884</v>
       </c>
       <c r="B556" t="n">
@@ -16575,7 +16563,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="2" t="n">
+      <c r="A557" s="1" t="n">
         <v>45891</v>
       </c>
       <c r="B557" t="n">
@@ -16604,7 +16592,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="2" t="n">
+      <c r="A558" s="1" t="n">
         <v>45898</v>
       </c>
       <c r="B558" t="n">
@@ -16633,7 +16621,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="2" t="n">
+      <c r="A559" s="1" t="n">
         <v>45905</v>
       </c>
       <c r="B559" t="n">
@@ -16662,7 +16650,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="2" t="n">
+      <c r="A560" s="1" t="n">
         <v>45912</v>
       </c>
       <c r="B560" t="n">
@@ -16691,7 +16679,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="2" t="n">
+      <c r="A561" s="1" t="n">
         <v>45919</v>
       </c>
       <c r="B561" t="n">
@@ -16720,7 +16708,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="2" t="n">
+      <c r="A562" s="1" t="n">
         <v>45926</v>
       </c>
       <c r="B562" t="n">
@@ -16749,7 +16737,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="2" t="n">
+      <c r="A563" s="1" t="n">
         <v>45933</v>
       </c>
       <c r="B563" t="n">
@@ -16778,7 +16766,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="2" t="n">
+      <c r="A564" s="1" t="n">
         <v>45940</v>
       </c>
       <c r="B564" t="n">
@@ -16807,7 +16795,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="2" t="n">
+      <c r="A565" s="1" t="n">
         <v>45947</v>
       </c>
       <c r="B565" t="n">
@@ -16836,7 +16824,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="2" t="n">
+      <c r="A566" s="1" t="n">
         <v>45954</v>
       </c>
       <c r="B566" t="n">
@@ -16865,7 +16853,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="2" t="n">
+      <c r="A567" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B567" t="n">
@@ -16894,7 +16882,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="2" t="n">
+      <c r="A568" s="1" t="n">
         <v>45968</v>
       </c>
       <c r="B568" t="n">
@@ -16923,7 +16911,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="2" t="n">
+      <c r="A569" s="1" t="n">
         <v>45975</v>
       </c>
       <c r="B569" t="n">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="2" t="n">
+      <c r="A570" s="1" t="n">
         <v>45982</v>
       </c>
       <c r="B570" t="n">
@@ -16981,7 +16969,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="2" t="n">
+      <c r="A571" s="1" t="n">
         <v>45989</v>
       </c>
       <c r="B571" t="n">
@@ -17010,7 +16998,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="2" t="n">
+      <c r="A572" s="1" t="n">
         <v>45996</v>
       </c>
       <c r="B572" t="n">
@@ -17039,7 +17027,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="2" t="n">
+      <c r="A573" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="B573" t="n">
@@ -17068,7 +17056,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="2" t="n">
+      <c r="A574" s="1" t="n">
         <v>46010</v>
       </c>
       <c r="B574" t="n">
@@ -17097,7 +17085,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="2" t="n">
+      <c r="A575" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="B575" t="n">
@@ -17126,7 +17114,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="2" t="n">
+      <c r="A576" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="B576" t="n">
@@ -17155,7 +17143,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="2" t="n">
+      <c r="A577" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B577" t="n">
@@ -17184,7 +17172,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="2" t="n">
+      <c r="A578" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="B578" t="n">
@@ -17213,7 +17201,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="2" t="n">
+      <c r="A579" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="B579" t="n">
@@ -17242,7 +17230,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="2" t="n">
+      <c r="A580" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="B580" t="n">
@@ -17271,7 +17259,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="2" t="n">
+      <c r="A581" s="1" t="n">
         <v>46059</v>
       </c>
       <c r="B581" t="n">
@@ -17300,7 +17288,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="2" t="n">
+      <c r="A582" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="B582" t="n">
@@ -17329,7 +17317,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="2" t="n">
+      <c r="A583" s="1" t="n">
         <v>46073</v>
       </c>
       <c r="B583" t="n">
@@ -17358,7 +17346,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="2" t="n">
+      <c r="A584" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="B584" t="n">
@@ -17387,7 +17375,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="2" t="n">
+      <c r="A585" s="1" t="n">
         <v>46087</v>
       </c>
       <c r="B585" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="2" t="n">
+      <c r="A586" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="B586" t="n">
@@ -17445,7 +17433,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="2" t="n">
+      <c r="A587" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="B587" t="n">
@@ -17474,7 +17462,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="2" t="n">
+      <c r="A588" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="B588" t="n">
@@ -17503,7 +17491,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="2" t="n">
+      <c r="A589" s="1" t="n">
         <v>46115</v>
       </c>
       <c r="B589" t="n">
@@ -17532,7 +17520,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="2" t="n">
+      <c r="A590" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="B590" t="n">
@@ -17561,7 +17549,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="2" t="n">
+      <c r="A591" s="1" t="n">
         <v>46129</v>
       </c>
       <c r="B591" t="n">
@@ -17590,7 +17578,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="2" t="n">
+      <c r="A592" s="1" t="n">
         <v>46136</v>
       </c>
       <c r="B592" t="n">
@@ -17619,7 +17607,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="2" t="n">
+      <c r="A593" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B593" t="n">
@@ -17648,7 +17636,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="2" t="n">
+      <c r="A594" s="1" t="n">
         <v>46150</v>
       </c>
       <c r="B594" t="n">
@@ -17677,7 +17665,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="2" t="n">
+      <c r="A595" s="1" t="n">
         <v>46157</v>
       </c>
       <c r="B595" t="n">
@@ -17706,7 +17694,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="2" t="n">
+      <c r="A596" s="1" t="n">
         <v>46164</v>
       </c>
       <c r="B596" t="n">
@@ -17735,7 +17723,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="2" t="n">
+      <c r="A597" s="1" t="n">
         <v>46171</v>
       </c>
       <c r="B597" t="n">
@@ -17764,7 +17752,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="2" t="n">
+      <c r="A598" s="1" t="n">
         <v>46178</v>
       </c>
       <c r="B598" t="n">
@@ -17793,7 +17781,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="2" t="n">
+      <c r="A599" s="1" t="n">
         <v>46185</v>
       </c>
       <c r="B599" t="n">
@@ -17822,7 +17810,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="2" t="n">
+      <c r="A600" s="1" t="n">
         <v>46192</v>
       </c>
       <c r="B600" t="n">
@@ -17851,7 +17839,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="2" t="n">
+      <c r="A601" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="B601" t="n">
@@ -17880,7 +17868,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="2" t="n">
+      <c r="A602" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="B602" t="n">
@@ -17909,7 +17897,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="2" t="n">
+      <c r="A603" s="1" t="n">
         <v>46213</v>
       </c>
       <c r="B603" t="n">
@@ -17938,7 +17926,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="2" t="n">
+      <c r="A604" s="1" t="n">
         <v>46220</v>
       </c>
       <c r="B604" t="n">
@@ -17967,7 +17955,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="2" t="n">
+      <c r="A605" s="1" t="n">
         <v>46227</v>
       </c>
       <c r="B605" t="n">
@@ -17996,7 +17984,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="2" t="n">
+      <c r="A606" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B606" t="n">
@@ -18025,7 +18013,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="2" t="n">
+      <c r="A607" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="B607" t="n">
@@ -18054,7 +18042,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="2" t="n">
+      <c r="A608" s="1" t="n">
         <v>46248</v>
       </c>
       <c r="B608" t="n">
@@ -18083,7 +18071,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="2" t="n">
+      <c r="A609" s="1" t="n">
         <v>46255</v>
       </c>
       <c r="B609" t="n">

--- a/yabanci para hareketi/dth.xlsx
+++ b/yabanci para hareketi/dth.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I609"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18099,6 +18099,35 @@
         <v>24.648</v>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B610" t="n">
+        <v>-2714.76188</v>
+      </c>
+      <c r="C610" t="n">
+        <v>-637.884295</v>
+      </c>
+      <c r="D610" t="n">
+        <v>-2076.877585</v>
+      </c>
+      <c r="E610" t="n">
+        <v>-653.04</v>
+      </c>
+      <c r="F610" t="n">
+        <v>15.155705</v>
+      </c>
+      <c r="G610" t="n">
+        <v>-98.012</v>
+      </c>
+      <c r="H610" t="n">
+        <v>78.881705</v>
+      </c>
+      <c r="I610" t="n">
+        <v>34.286</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
